--- a/伊藤工数表.xlsx
+++ b/伊藤工数表.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="435" windowWidth="18315" windowHeight="11535" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="750" windowWidth="18315" windowHeight="11220" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="原紙(入力)" sheetId="5" r:id="rId1"/>
-    <sheet name="2017.1" sheetId="4" r:id="rId2"/>
-    <sheet name="2017.2" sheetId="6" r:id="rId3"/>
-    <sheet name="2017.12" sheetId="8" r:id="rId4"/>
+    <sheet name="2017.1" sheetId="9" r:id="rId2"/>
+    <sheet name="2017.2" sheetId="10" r:id="rId3"/>
+    <sheet name="2017.12" sheetId="11" r:id="rId4"/>
+    <sheet name="入力規則" sheetId="14" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'2017.1'!$B$3:$I$58</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="162">
   <si>
     <t>end4</t>
     <phoneticPr fontId="1"/>
@@ -267,9 +268,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員</t>
-  </si>
-  <si>
     <t>first1</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -328,31 +326,274 @@
     <t>HH16-0019</t>
   </si>
   <si>
-    <t>END</t>
-  </si>
-  <si>
-    <t>END</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MM-D72C</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>DSE-6ADG</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>DSE-6ADG</t>
+    <t>社員</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ＰＧＳ２－２０／３０ＶＣＷ－４／０,ＰＧＳ５－２０／３０ＶＣＰＷ－４／０,ＳＰＡＣ－Ｇ２０／３０Ｂ,ＳＰＡＣ－Ｇ２０／３０Ｃ,ＫＬ－Ｐ,ＰＶＳ１０－６ＬＦ－４／０,ＲＭＤ２（－Ｆ７）,ＭＭ－Ｄ４１（一般向け）,ＭＭ－Ｄ４１Ｇ（関電向け）,ＭＭ－Ｄ４１　鎖錠装置取付作業,ＭＭ－Ｄ４３,ＭＭ－Ｄ５１ＢＬ,ＭＭ－Ｄ７１Ａ,ＭＭ－Ｄ７２Ａ,ＭＭ－Ｄ７２Ｂ,ＭＭ－Ｄ７２Ｃ,ＲＨ－ＤＬ,ＲＨ－ＤＬ（関電仕様）,ＲＨ－ＤＬ（前橋向け）,ＲＨ－ＤＮ,ＲＨ－Ｄ,ＲＨ－ＥＬ,ＲＨ－Ｆ(Ｌ),ＲＨ－ＨＬ１,ＤＳＣ－６Ａ,ＤＳＣ－６ＡＢ,地上設置型変圧器箱,INV,ＰＶＳ２０－６ＶＦ－４／０,ＭＫ－７,工事車,外箱,バッテリー組立,メガセーフ１バンク分（ｺﾝﾃﾞﾝｻ60set、INV18set）,ＤＳＣ－６Ｂ,ＤＳＣ－６ＡＤ,ＤＳＣ－６ＢＤ,ＤＳＣ－６ＢＢ,ＤＳＣ－６ＣＤ,ＤＳＣ－１０ＢＢ,ＤＳＣ－１０ＢＤ,ＤＳＣ－２１ＡＢ,ＤＳＣ－２１ＡＤ,ＤＳＣ－２１ＡＤＧ（負荷側接地）,ＤＳＣ－２１ＡＤＧ（電源側接地）,ＤＳＣ－２１ＡＤＳ,ＤＳＣ－３０ＢＤ,ＤＳＣ－３１ＡＤ,ＤＳＣ－３１ＡＤＧ（電源側接地）,ＤＳＣ－３１ＡＤＳ,ＤＳＥ－６ＡＶ,ＤＳＥ－６ＡＶ－４Ｌ／Ｒ２（２極断路器）,ＤＳＥ－６ＡＤＧ,ＤＳＥ２－６ＡＶ,ＤＳＥ３－６ＡＶ,ＤＳＥ－８Ｇ,ＤＳＥ－２０ＡＶ,ＤＳＥ－２０ＡＶＧ,ＤＳＥ－２０ＡＶＧＳ,ＤＳＥ－２１ＡＤ,ＤＳＥ－３０ＡＶ,ＤＳＥ－３０ＡＶＧ,ＤＳＥ－３０ＡＶＧＳ,ＧＤＳＥ－８Ｇ,ＬＤＳ－２０ＡＶ,ＬＤＳ－３０ＡＶ,ＮＲＤＳ－３０ＦＧＳ,首都高用</t>
-    <phoneticPr fontId="1"/>
+    <t>first1</t>
+  </si>
+  <si>
+    <t>HH16-0047</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>DSE3-6AV</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>DSC-6AB</t>
+  </si>
+  <si>
+    <t>HH16-0041</t>
+  </si>
+  <si>
+    <t>B0</t>
+  </si>
+  <si>
+    <t>ＩＮＶ</t>
+  </si>
+  <si>
+    <t>INV</t>
+  </si>
+  <si>
+    <t>last</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>end2</t>
+  </si>
+  <si>
+    <t>end3</t>
+  </si>
+  <si>
+    <t>end4</t>
+  </si>
+  <si>
+    <t>end5</t>
+  </si>
+  <si>
+    <t>end6</t>
+  </si>
+  <si>
+    <t>ＰＧＳ２－２０／３０ＶＣＷ－４／０</t>
+  </si>
+  <si>
+    <t>ＰＧＳ５－２０／３０ＶＣＰＷ－４／０</t>
+  </si>
+  <si>
+    <t>ＳＰＡＣ－Ｇ２０／３０Ｂ</t>
+  </si>
+  <si>
+    <t>ＳＰＡＣ－Ｇ２０／３０Ｃ</t>
+  </si>
+  <si>
+    <t>ＫＬ－Ｐ</t>
+  </si>
+  <si>
+    <t>ＰＶＳ１０－６ＬＦ－４／０</t>
+  </si>
+  <si>
+    <t>ＲＭＤ２（－Ｆ７）</t>
+  </si>
+  <si>
+    <t>ＭＭ－Ｄ４１（一般向け）</t>
+  </si>
+  <si>
+    <t>ＭＭ－Ｄ４１Ｇ（関電向け）</t>
+  </si>
+  <si>
+    <t>ＭＭ－Ｄ４１　鎖錠装置取付作業</t>
+  </si>
+  <si>
+    <t>ＭＭ－Ｄ４３</t>
+  </si>
+  <si>
+    <t>ＭＭ－Ｄ５１ＢＬ</t>
+  </si>
+  <si>
+    <t>ＭＭ－Ｄ７１Ａ</t>
+  </si>
+  <si>
+    <t>ＭＭ－Ｄ７２Ａ</t>
+  </si>
+  <si>
+    <t>ＭＭ－Ｄ７２Ｂ</t>
+  </si>
+  <si>
+    <t>ＭＭ－Ｄ７２Ｃ</t>
+  </si>
+  <si>
+    <t>ＲＨ－ＤＬ</t>
+  </si>
+  <si>
+    <t>ＲＨ－ＤＬ（関電仕様）</t>
+  </si>
+  <si>
+    <t>ＲＨ－ＤＬ（前橋向け）</t>
+  </si>
+  <si>
+    <t>ＲＨ－ＤＮ</t>
+  </si>
+  <si>
+    <t>ＲＨ－Ｄ</t>
+  </si>
+  <si>
+    <t>ＲＨ－ＥＬ</t>
+  </si>
+  <si>
+    <t>ＲＨ－Ｆ(Ｌ)</t>
+  </si>
+  <si>
+    <t>ＲＨ－ＨＬ１</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－６Ａ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－６ＡＢ</t>
+  </si>
+  <si>
+    <t>地上設置型変圧器箱</t>
+  </si>
+  <si>
+    <t>ＰＶＳ２０－６ＶＦ－４／０</t>
+  </si>
+  <si>
+    <t>ＭＫ－７</t>
+  </si>
+  <si>
+    <t>工事車</t>
+  </si>
+  <si>
+    <t>外箱</t>
+  </si>
+  <si>
+    <t>バッテリー組立</t>
+  </si>
+  <si>
+    <t>メガセーフ１バンク分
+（ｺﾝﾃﾞﾝｻ60set、INV18set）</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－６Ｂ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－６ＡＤ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－６ＢＤ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－６ＢＢ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－６ＣＤ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－１０ＢＢ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－１０ＢＤ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－２１ＡＢ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－２１ＡＤ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－２１ＡＤＧ（負荷側接地）</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－２１ＡＤＧ（電源側接地）</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－２１ＡＤＳ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－３０ＢＤ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－３１ＡＤ</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－３１ＡＤＧ（電源側接地）</t>
+  </si>
+  <si>
+    <t>ＤＳＣ－３１ＡＤＳ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－６ＡＶ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－６ＡＶ－４Ｌ／Ｒ２（２極断路器）</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－６ＡＤＧ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ２－６ＡＶ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ３－６ＡＶ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－８Ｇ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－２０ＡＶ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－２０ＡＶＧ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－２０ＡＶＧＳ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－２１ＡＤ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－３０ＡＶ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－３０ＡＶＧ</t>
+  </si>
+  <si>
+    <t>ＤＳＥ－３０ＡＶＧＳ</t>
+  </si>
+  <si>
+    <t>ＧＤＳＥ－８Ｇ</t>
+  </si>
+  <si>
+    <t>ＬＤＳ－２０ＡＶ</t>
+  </si>
+  <si>
+    <t>ＬＤＳ－３０ＡＶ</t>
+  </si>
+  <si>
+    <t>ＮＲＤＳ－３０ＦＧＳ</t>
+  </si>
+  <si>
+    <t>首都高用</t>
+  </si>
+  <si>
+    <t>派遣</t>
+  </si>
+  <si>
+    <t>aa</t>
   </si>
 </sst>
 </file>
@@ -360,8 +601,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
-    <numFmt numFmtId="176" formatCode="m/d;@"/>
+    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
+    <numFmt numFmtId="177" formatCode="m/d;@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -517,7 +758,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="40">
@@ -551,7 +792,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
@@ -569,7 +810,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
@@ -585,7 +826,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -614,14 +855,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1074,7 +1315,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6172200" y="10353675"/>
+          <a:off x="9496425" y="10467975"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1146,7 +1387,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2057400" y="10363200"/>
+          <a:off x="1609725" y="10477500"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1218,7 +1459,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6172200" y="10353675"/>
+          <a:off x="9496425" y="10467975"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1290,7 +1531,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6172200" y="10353675"/>
+          <a:off x="9496425" y="10467975"/>
           <a:ext cx="19050" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1340,7 +1581,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2057400" y="10363200"/>
+          <a:off x="1609725" y="10477500"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1412,7 +1653,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6172200" y="10353675"/>
+          <a:off x="9496425" y="10467975"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2610,10 +2851,7 @@
     <row r="2" spans="1:9">
       <c r="A2" s="36"/>
       <c r="B2" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21.75" customHeight="1">
@@ -3205,9 +3443,7 @@
       <c r="B59" s="12"/>
       <c r="C59" s="11"/>
       <c r="D59" s="6"/>
-      <c r="E59" s="11" t="s">
-        <v>75</v>
-      </c>
+      <c r="E59" s="11"/>
       <c r="F59" s="10"/>
       <c r="G59" s="9"/>
       <c r="H59" s="8"/>
@@ -3240,14 +3476,1301 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>"社員,派遣"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="81" orientation="portrait" verticalDpi="4294967293" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>入力規則!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>E4:E58</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:J117"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12" style="4" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="7.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="41.25" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="B1" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="36"/>
+      <c r="B2" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="21.75" customHeight="1">
+      <c r="B3" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="B4" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="28">
+        <v>5.12</v>
+      </c>
+      <c r="G4" s="27"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="B5" s="26">
+        <v>43041</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="28">
+        <v>6.03</v>
+      </c>
+      <c r="G5" s="27"/>
+      <c r="H5" s="32">
+        <v>3</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="B6" s="26">
+        <v>43041</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="28">
+        <v>6.03</v>
+      </c>
+      <c r="G6" s="27"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="14"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="B7" s="26">
+        <v>43044</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="28"/>
+      <c r="G7" s="27">
+        <v>4</v>
+      </c>
+      <c r="H7" s="21"/>
+      <c r="I7" s="14"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8" s="26">
+        <v>43045</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="28">
+        <v>6.03</v>
+      </c>
+      <c r="G8" s="27"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" s="26">
+        <v>43054</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="28">
+        <v>5</v>
+      </c>
+      <c r="G9" s="27"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="14"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="26">
+        <v>43055</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="28">
+        <v>6.03</v>
+      </c>
+      <c r="G10" s="27"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="14"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="26">
+        <v>43047</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="28">
+        <v>8.2219999999999995</v>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="14"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" s="26">
+        <v>43046</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="28"/>
+      <c r="G12" s="27">
+        <v>5</v>
+      </c>
+      <c r="H12" s="21"/>
+      <c r="I12" s="14"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="26">
+        <v>43062</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="27">
+        <v>1</v>
+      </c>
+      <c r="H13" s="21"/>
+      <c r="I13" s="14"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14" s="26">
+        <v>43045</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="28">
+        <v>8</v>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="26">
+        <v>43048</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="28">
+        <v>8</v>
+      </c>
+      <c r="G15" s="27"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="26">
+        <v>43048</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="28">
+        <v>8</v>
+      </c>
+      <c r="G16" s="27"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="28">
+        <v>5</v>
+      </c>
+      <c r="G17" s="27"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="28">
+        <v>5</v>
+      </c>
+      <c r="G18" s="27"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="14"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="28">
+        <v>5</v>
+      </c>
+      <c r="G19" s="27"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="28">
+        <v>5</v>
+      </c>
+      <c r="G20" s="27"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="14"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="28">
+        <v>5</v>
+      </c>
+      <c r="G21" s="27"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="14"/>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="28">
+        <v>5</v>
+      </c>
+      <c r="G22" s="27"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="14"/>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="28">
+        <v>5</v>
+      </c>
+      <c r="G23" s="27"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="14"/>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="28">
+        <v>5</v>
+      </c>
+      <c r="G24" s="27"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="14"/>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="28">
+        <v>5</v>
+      </c>
+      <c r="G25" s="27"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="14"/>
+    </row>
+    <row r="26" spans="2:9" ht="14.25" customHeight="1">
+      <c r="B26" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="28">
+        <v>5</v>
+      </c>
+      <c r="G26" s="27"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="14"/>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="28">
+        <v>5</v>
+      </c>
+      <c r="G27" s="27"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="14"/>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="28">
+        <v>5</v>
+      </c>
+      <c r="G28" s="27"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="14"/>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="28">
+        <v>5</v>
+      </c>
+      <c r="G29" s="27"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="14"/>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="28">
+        <v>5</v>
+      </c>
+      <c r="G30" s="27"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="14"/>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="28">
+        <v>5</v>
+      </c>
+      <c r="G31" s="27"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="14"/>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="28">
+        <v>5</v>
+      </c>
+      <c r="G32" s="27"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="14"/>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="28">
+        <v>5</v>
+      </c>
+      <c r="G33" s="27"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="28">
+        <v>5</v>
+      </c>
+      <c r="G34" s="27"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="14"/>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="28">
+        <v>5</v>
+      </c>
+      <c r="G35" s="27"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="14"/>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="28">
+        <v>5</v>
+      </c>
+      <c r="G36" s="27"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="14"/>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="28">
+        <v>5</v>
+      </c>
+      <c r="G37" s="27"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="14"/>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="28">
+        <v>5</v>
+      </c>
+      <c r="G38" s="27"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="14"/>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="28">
+        <v>5</v>
+      </c>
+      <c r="G39" s="27"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="14"/>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="28">
+        <v>5</v>
+      </c>
+      <c r="G40" s="27"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="14"/>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="28">
+        <v>5</v>
+      </c>
+      <c r="G41" s="27"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="28">
+        <v>5</v>
+      </c>
+      <c r="G42" s="27"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="23">
+        <v>5</v>
+      </c>
+      <c r="G43" s="22"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="28">
+        <v>5</v>
+      </c>
+      <c r="G44" s="27"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="28">
+        <v>5</v>
+      </c>
+      <c r="G45" s="27"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="28">
+        <v>5</v>
+      </c>
+      <c r="G46" s="27"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="23">
+        <v>5</v>
+      </c>
+      <c r="G47" s="22"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="23">
+        <v>5</v>
+      </c>
+      <c r="G48" s="22"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="B49" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="23">
+        <v>5</v>
+      </c>
+      <c r="G49" s="22"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" s="13" customFormat="1">
+      <c r="B50" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="23">
+        <v>5</v>
+      </c>
+      <c r="G50" s="22"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="23">
+        <v>5</v>
+      </c>
+      <c r="G51" s="22"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="23">
+        <v>5</v>
+      </c>
+      <c r="G52" s="22"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="F53" s="23">
+        <v>5</v>
+      </c>
+      <c r="G53" s="22"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J53" s="13"/>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="23">
+        <v>5</v>
+      </c>
+      <c r="G54" s="22"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="13"/>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="23">
+        <v>5</v>
+      </c>
+      <c r="G55" s="22"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J55" s="13"/>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="23">
+        <v>5</v>
+      </c>
+      <c r="G56" s="22"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J56" s="13"/>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="B57" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="23">
+        <v>5</v>
+      </c>
+      <c r="G57" s="22"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" s="13"/>
+    </row>
+    <row r="58" spans="2:10">
+      <c r="B58" s="20">
+        <v>43040</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F58" s="17">
+        <v>5</v>
+      </c>
+      <c r="G58" s="16"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="13"/>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="B59" s="12"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="7"/>
+    </row>
+    <row r="61" spans="2:10" ht="27" customHeight="1"/>
+    <row r="110" spans="2:2">
+      <c r="B110" s="5"/>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="5"/>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="6"/>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="5"/>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" s="6"/>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="5"/>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="6"/>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>"社員,派遣"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="81" orientation="portrait" verticalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>入力規則!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>E4:E58</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J117"/>
@@ -3272,7 +4795,7 @@
     <row r="2" spans="1:9">
       <c r="A2" s="36"/>
       <c r="B2" s="4" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21.75" customHeight="1">
@@ -3306,1171 +4829,594 @@
         <v>43040</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="F4" s="28">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="G4" s="27"/>
       <c r="H4" s="21"/>
-      <c r="I4" s="33" t="s">
-        <v>55</v>
+      <c r="I4" s="38">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="26">
-        <v>43041</v>
+        <v>43040</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F5" s="28">
-        <v>6.03</v>
+        <v>5</v>
       </c>
       <c r="G5" s="27"/>
-      <c r="H5" s="32">
-        <v>3</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>41</v>
+      <c r="H5" s="32"/>
+      <c r="I5" s="37">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="B6" s="26">
-        <v>43041</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="28">
-        <v>6.03</v>
-      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="28"/>
       <c r="G6" s="27"/>
       <c r="H6" s="21"/>
       <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="B7" s="26">
-        <v>43044</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="24"/>
       <c r="F7" s="28"/>
-      <c r="G7" s="27">
-        <v>4</v>
-      </c>
+      <c r="G7" s="27"/>
       <c r="H7" s="21"/>
       <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="B8" s="26">
-        <v>43045</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="28">
-        <v>6.03</v>
-      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="28"/>
       <c r="G8" s="27"/>
       <c r="H8" s="21"/>
       <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="B9" s="26">
-        <v>43054</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="28">
-        <v>5</v>
-      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="28"/>
       <c r="G9" s="27"/>
       <c r="H9" s="21"/>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="B10" s="26">
-        <v>43055</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="28">
-        <v>6.03</v>
-      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="28"/>
       <c r="G10" s="27"/>
       <c r="H10" s="21"/>
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="B11" s="26">
-        <v>43047</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="28">
-        <v>8.2219999999999995</v>
-      </c>
+      <c r="B11" s="26"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="27"/>
       <c r="H11" s="21"/>
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="B12" s="26">
-        <v>43046</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="27">
-        <v>5</v>
-      </c>
+      <c r="G12" s="27"/>
       <c r="H12" s="21"/>
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="B13" s="26">
-        <v>43062</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>33</v>
-      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="28"/>
-      <c r="G13" s="27">
-        <v>1</v>
-      </c>
+      <c r="G13" s="27"/>
       <c r="H13" s="21"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="B14" s="26">
-        <v>43045</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="28">
-        <v>8</v>
-      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="27"/>
       <c r="H14" s="21"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="B15" s="26">
-        <v>43048</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="28">
-        <v>8</v>
-      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="27"/>
       <c r="H15" s="21"/>
-      <c r="I15" s="14" t="s">
-        <v>30</v>
-      </c>
+      <c r="I15" s="14"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="B16" s="26">
-        <v>43048</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="28">
-        <v>8</v>
-      </c>
+      <c r="B16" s="26"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="27"/>
       <c r="H16" s="21"/>
       <c r="I16" s="14"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="28">
-        <v>5</v>
-      </c>
+      <c r="B17" s="26"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="28"/>
       <c r="G17" s="27"/>
       <c r="H17" s="21"/>
       <c r="I17" s="14"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="28">
-        <v>5</v>
-      </c>
+      <c r="B18" s="26"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="28"/>
       <c r="G18" s="27"/>
       <c r="H18" s="21"/>
       <c r="I18" s="14"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="28">
-        <v>5</v>
-      </c>
+      <c r="B19" s="26"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="28"/>
       <c r="G19" s="27"/>
       <c r="H19" s="21"/>
       <c r="I19" s="14"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="28">
-        <v>5</v>
-      </c>
+      <c r="B20" s="26"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="28"/>
       <c r="G20" s="27"/>
       <c r="H20" s="21"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="28">
-        <v>5</v>
-      </c>
+      <c r="B21" s="26"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="28"/>
       <c r="G21" s="27"/>
       <c r="H21" s="21"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="28">
-        <v>5</v>
-      </c>
+      <c r="B22" s="26"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="28"/>
       <c r="G22" s="27"/>
       <c r="H22" s="21"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="28">
-        <v>5</v>
-      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="28"/>
       <c r="G23" s="27"/>
       <c r="H23" s="21"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="28">
-        <v>5</v>
-      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="28"/>
       <c r="G24" s="27"/>
       <c r="H24" s="21"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="28">
-        <v>5</v>
-      </c>
+      <c r="B25" s="26"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="28"/>
       <c r="G25" s="27"/>
       <c r="H25" s="21"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B26" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="28">
-        <v>5</v>
-      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="28"/>
       <c r="G26" s="27"/>
       <c r="H26" s="21"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="28">
-        <v>5</v>
-      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="28"/>
       <c r="G27" s="27"/>
       <c r="H27" s="21"/>
       <c r="I27" s="14"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="28">
-        <v>5</v>
-      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="28"/>
       <c r="G28" s="27"/>
       <c r="H28" s="21"/>
       <c r="I28" s="14"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="28">
-        <v>5</v>
-      </c>
+      <c r="B29" s="26"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="28"/>
       <c r="G29" s="27"/>
       <c r="H29" s="21"/>
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="28">
-        <v>5</v>
-      </c>
+      <c r="B30" s="26"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="28"/>
       <c r="G30" s="27"/>
       <c r="H30" s="21"/>
       <c r="I30" s="14"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="28">
-        <v>5</v>
-      </c>
+      <c r="B31" s="26"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="27"/>
       <c r="H31" s="21"/>
       <c r="I31" s="14"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="28">
-        <v>5</v>
-      </c>
+      <c r="B32" s="26"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="28"/>
       <c r="G32" s="27"/>
       <c r="H32" s="21"/>
       <c r="I32" s="14"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="28">
-        <v>5</v>
-      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="28"/>
       <c r="G33" s="27"/>
       <c r="H33" s="21"/>
-      <c r="I33" s="14" t="s">
-        <v>26</v>
-      </c>
+      <c r="I33" s="14"/>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="28">
-        <v>5</v>
-      </c>
+      <c r="B34" s="26"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="28"/>
       <c r="G34" s="27"/>
       <c r="H34" s="21"/>
       <c r="I34" s="14"/>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="28">
-        <v>5</v>
-      </c>
+      <c r="B35" s="26"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="28"/>
       <c r="G35" s="27"/>
       <c r="H35" s="21"/>
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="28">
-        <v>5</v>
-      </c>
+      <c r="B36" s="26"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="28"/>
       <c r="G36" s="27"/>
       <c r="H36" s="21"/>
       <c r="I36" s="14"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="28">
-        <v>5</v>
-      </c>
+      <c r="B37" s="26"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="28"/>
       <c r="G37" s="27"/>
       <c r="H37" s="21"/>
       <c r="I37" s="14"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="28">
-        <v>5</v>
-      </c>
+      <c r="B38" s="26"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="28"/>
       <c r="G38" s="27"/>
       <c r="H38" s="21"/>
       <c r="I38" s="14"/>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="28">
-        <v>5</v>
-      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="28"/>
       <c r="G39" s="27"/>
       <c r="H39" s="21"/>
       <c r="I39" s="14"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="28">
-        <v>5</v>
-      </c>
+      <c r="B40" s="26"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="28"/>
       <c r="G40" s="27"/>
       <c r="H40" s="21"/>
       <c r="I40" s="14"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E41" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="28">
-        <v>5</v>
-      </c>
+      <c r="B41" s="26"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="28"/>
       <c r="G41" s="27"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="I41" s="14"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="28">
-        <v>5</v>
-      </c>
+      <c r="B42" s="26"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="28"/>
       <c r="G42" s="27"/>
       <c r="H42" s="21"/>
-      <c r="I42" s="14" t="s">
-        <v>24</v>
-      </c>
+      <c r="I42" s="14"/>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="23">
-        <v>5</v>
-      </c>
+      <c r="B43" s="26"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="23"/>
       <c r="G43" s="22"/>
       <c r="H43" s="21"/>
-      <c r="I43" s="14" t="s">
-        <v>4</v>
-      </c>
+      <c r="I43" s="14"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="28">
-        <v>5</v>
-      </c>
+      <c r="B44" s="26"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="28"/>
       <c r="G44" s="27"/>
       <c r="H44" s="21"/>
-      <c r="I44" s="14" t="s">
-        <v>0</v>
-      </c>
+      <c r="I44" s="14"/>
     </row>
     <row r="45" spans="2:9">
-      <c r="B45" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="28">
-        <v>5</v>
-      </c>
+      <c r="B45" s="26"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="28"/>
       <c r="G45" s="27"/>
       <c r="H45" s="21"/>
-      <c r="I45" s="14" t="s">
-        <v>23</v>
-      </c>
+      <c r="I45" s="14"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="28">
-        <v>5</v>
-      </c>
+      <c r="B46" s="26"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="28"/>
       <c r="G46" s="27"/>
       <c r="H46" s="21"/>
-      <c r="I46" s="14" t="s">
-        <v>22</v>
-      </c>
+      <c r="I46" s="14"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="23">
-        <v>5</v>
-      </c>
+      <c r="B47" s="26"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="23"/>
       <c r="G47" s="22"/>
       <c r="H47" s="21"/>
-      <c r="I47" s="14" t="s">
-        <v>21</v>
-      </c>
+      <c r="I47" s="14"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="23">
-        <v>5</v>
-      </c>
+      <c r="B48" s="26"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="22"/>
       <c r="H48" s="21"/>
-      <c r="I48" s="14" t="s">
-        <v>20</v>
-      </c>
+      <c r="I48" s="14"/>
     </row>
     <row r="49" spans="2:10">
-      <c r="B49" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="23">
-        <v>5</v>
-      </c>
+      <c r="B49" s="26"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="23"/>
       <c r="G49" s="22"/>
       <c r="H49" s="21"/>
-      <c r="I49" s="14" t="s">
-        <v>19</v>
-      </c>
+      <c r="I49" s="14"/>
     </row>
     <row r="50" spans="2:10" s="13" customFormat="1">
-      <c r="B50" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="23">
-        <v>5</v>
-      </c>
+      <c r="B50" s="26"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="23"/>
       <c r="G50" s="22"/>
       <c r="H50" s="21"/>
-      <c r="I50" s="14" t="s">
-        <v>18</v>
-      </c>
+      <c r="I50" s="14"/>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="2:10">
-      <c r="B51" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="23">
-        <v>5</v>
-      </c>
+      <c r="B51" s="26"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="23"/>
       <c r="G51" s="22"/>
       <c r="H51" s="21"/>
-      <c r="I51" s="14" t="s">
-        <v>17</v>
-      </c>
+      <c r="I51" s="14"/>
       <c r="J51" s="13"/>
     </row>
     <row r="52" spans="2:10">
-      <c r="B52" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E52" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="23">
-        <v>5</v>
-      </c>
+      <c r="B52" s="26"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="23"/>
       <c r="G52" s="22"/>
       <c r="H52" s="21"/>
-      <c r="I52" s="14" t="s">
-        <v>15</v>
-      </c>
+      <c r="I52" s="14"/>
       <c r="J52" s="13"/>
     </row>
     <row r="53" spans="2:10">
-      <c r="B53" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="F53" s="23">
-        <v>5</v>
-      </c>
+      <c r="B53" s="26"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="23"/>
       <c r="G53" s="22"/>
       <c r="H53" s="21"/>
-      <c r="I53" s="14" t="s">
-        <v>14</v>
-      </c>
+      <c r="I53" s="14"/>
       <c r="J53" s="13"/>
     </row>
     <row r="54" spans="2:10">
-      <c r="B54" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="23">
-        <v>5</v>
-      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="23"/>
       <c r="G54" s="22"/>
       <c r="H54" s="21"/>
-      <c r="I54" s="14" t="s">
-        <v>13</v>
-      </c>
+      <c r="I54" s="14"/>
       <c r="J54" s="13"/>
     </row>
     <row r="55" spans="2:10">
-      <c r="B55" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="23">
-        <v>5</v>
-      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="23"/>
       <c r="G55" s="22"/>
       <c r="H55" s="21"/>
-      <c r="I55" s="14" t="s">
-        <v>12</v>
-      </c>
+      <c r="I55" s="14"/>
       <c r="J55" s="13"/>
     </row>
     <row r="56" spans="2:10">
-      <c r="B56" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="23">
-        <v>5</v>
-      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="23"/>
       <c r="G56" s="22"/>
       <c r="H56" s="21"/>
-      <c r="I56" s="14" t="s">
-        <v>11</v>
-      </c>
+      <c r="I56" s="14"/>
       <c r="J56" s="13"/>
     </row>
     <row r="57" spans="2:10">
-      <c r="B57" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="F57" s="23">
-        <v>5</v>
-      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="23"/>
       <c r="G57" s="22"/>
       <c r="H57" s="21"/>
-      <c r="I57" s="14" t="s">
-        <v>9</v>
-      </c>
+      <c r="I57" s="14"/>
       <c r="J57" s="13"/>
     </row>
     <row r="58" spans="2:10">
-      <c r="B58" s="20">
-        <v>43040</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" s="17">
-        <v>5</v>
-      </c>
+      <c r="B58" s="20"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="17"/>
       <c r="G58" s="16"/>
       <c r="H58" s="15"/>
-      <c r="I58" s="14" t="s">
-        <v>5</v>
-      </c>
+      <c r="I58" s="14"/>
       <c r="J58" s="13"/>
     </row>
     <row r="59" spans="2:10">
       <c r="B59" s="12"/>
       <c r="C59" s="11"/>
       <c r="D59" s="6"/>
-      <c r="E59" s="11" t="s">
-        <v>74</v>
-      </c>
+      <c r="E59" s="11"/>
       <c r="F59" s="10"/>
       <c r="G59" s="9"/>
       <c r="H59" s="8"/>
       <c r="I59" s="7"/>
     </row>
-    <row r="60" spans="2:10">
-      <c r="B60" s="37"/>
-    </row>
     <row r="61" spans="2:10" ht="27" customHeight="1"/>
     <row r="110" spans="2:2">
       <c r="B110" s="5"/>
@@ -4498,14 +5444,31 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>"社員,派遣"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="81" orientation="portrait" verticalDpi="4294967293" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>入力規則!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>E4:E58</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:J117"/>
@@ -4530,7 +5493,7 @@
     <row r="2" spans="1:9">
       <c r="A2" s="36"/>
       <c r="B2" s="4" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21.75" customHeight="1">
@@ -4573,17 +5536,17 @@
         <v>1</v>
       </c>
       <c r="F4" s="28">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="G4" s="27"/>
       <c r="H4" s="21"/>
-      <c r="I4" s="39">
-        <v>2</v>
+      <c r="I4" s="33" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="26">
-        <v>43040</v>
+        <v>43041</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>3</v>
@@ -4595,560 +5558,1130 @@
         <v>1</v>
       </c>
       <c r="F5" s="28">
-        <v>5</v>
+        <v>6.03</v>
       </c>
       <c r="G5" s="27"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="38">
-        <v>2</v>
+      <c r="H5" s="32">
+        <v>3</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="B6" s="26"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="28"/>
+      <c r="B6" s="26">
+        <v>43041</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="28">
+        <v>6.03</v>
+      </c>
       <c r="G6" s="27"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="38"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="B7" s="26"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="24"/>
+      <c r="B7" s="26">
+        <v>43044</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>78</v>
+      </c>
       <c r="F7" s="28"/>
-      <c r="G7" s="27"/>
+      <c r="G7" s="27">
+        <v>4</v>
+      </c>
       <c r="H7" s="21"/>
       <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="B8" s="26"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="28"/>
+      <c r="B8" s="26">
+        <v>43045</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="28">
+        <v>6.03</v>
+      </c>
       <c r="G8" s="27"/>
       <c r="H8" s="21"/>
       <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="B9" s="26"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="28"/>
+      <c r="B9" s="26">
+        <v>43054</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="28">
+        <v>5</v>
+      </c>
       <c r="G9" s="27"/>
       <c r="H9" s="21"/>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="B10" s="26"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="28"/>
+      <c r="B10" s="26">
+        <v>43055</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="28">
+        <v>6.03</v>
+      </c>
       <c r="G10" s="27"/>
       <c r="H10" s="21"/>
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="B11" s="26"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="28"/>
+      <c r="B11" s="26">
+        <v>43047</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="28">
+        <v>8.2219999999999995</v>
+      </c>
       <c r="G11" s="27"/>
       <c r="H11" s="21"/>
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="B12" s="26"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="24"/>
+      <c r="B12" s="26">
+        <v>43046</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>78</v>
+      </c>
       <c r="F12" s="28"/>
-      <c r="G12" s="27"/>
+      <c r="G12" s="27">
+        <v>5</v>
+      </c>
       <c r="H12" s="21"/>
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="B13" s="26"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="24"/>
+      <c r="B13" s="26">
+        <v>43062</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>83</v>
+      </c>
       <c r="F13" s="28"/>
-      <c r="G13" s="27"/>
+      <c r="G13" s="27">
+        <v>1</v>
+      </c>
       <c r="H13" s="21"/>
       <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="B14" s="26"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="28"/>
+      <c r="B14" s="26">
+        <v>43045</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="28">
+        <v>8</v>
+      </c>
       <c r="G14" s="27"/>
       <c r="H14" s="21"/>
       <c r="I14" s="14"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="B15" s="26"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="28"/>
+      <c r="B15" s="26">
+        <v>43048</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="28">
+        <v>8</v>
+      </c>
       <c r="G15" s="27"/>
       <c r="H15" s="21"/>
-      <c r="I15" s="14"/>
+      <c r="I15" s="14" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="B16" s="26"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="28"/>
+      <c r="B16" s="26">
+        <v>43048</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="28">
+        <v>8</v>
+      </c>
       <c r="G16" s="27"/>
       <c r="H16" s="21"/>
       <c r="I16" s="14"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="26"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="28"/>
+      <c r="B17" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="28">
+        <v>5</v>
+      </c>
       <c r="G17" s="27"/>
       <c r="H17" s="21"/>
       <c r="I17" s="14"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="26"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="28"/>
+      <c r="B18" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="28">
+        <v>5</v>
+      </c>
       <c r="G18" s="27"/>
       <c r="H18" s="21"/>
       <c r="I18" s="14"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="26"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="28"/>
+      <c r="B19" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="28">
+        <v>5</v>
+      </c>
       <c r="G19" s="27"/>
       <c r="H19" s="21"/>
       <c r="I19" s="14"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="26"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="28">
+        <v>5</v>
+      </c>
       <c r="G20" s="27"/>
       <c r="H20" s="21"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="26"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="28"/>
+      <c r="B21" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="28">
+        <v>5</v>
+      </c>
       <c r="G21" s="27"/>
       <c r="H21" s="21"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="26"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="28"/>
+      <c r="B22" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="28">
+        <v>5</v>
+      </c>
       <c r="G22" s="27"/>
       <c r="H22" s="21"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="26"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="28"/>
+      <c r="B23" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="28">
+        <v>5</v>
+      </c>
       <c r="G23" s="27"/>
       <c r="H23" s="21"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="26"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="28"/>
+      <c r="B24" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="28">
+        <v>5</v>
+      </c>
       <c r="G24" s="27"/>
       <c r="H24" s="21"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="26"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="28"/>
+      <c r="B25" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="28">
+        <v>5</v>
+      </c>
       <c r="G25" s="27"/>
       <c r="H25" s="21"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B26" s="26"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="28"/>
+      <c r="B26" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="28">
+        <v>5</v>
+      </c>
       <c r="G26" s="27"/>
       <c r="H26" s="21"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="26"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="28"/>
+      <c r="B27" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="28">
+        <v>5</v>
+      </c>
       <c r="G27" s="27"/>
       <c r="H27" s="21"/>
       <c r="I27" s="14"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="26"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="28"/>
+      <c r="B28" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="28">
+        <v>5</v>
+      </c>
       <c r="G28" s="27"/>
       <c r="H28" s="21"/>
       <c r="I28" s="14"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="26"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="28"/>
+      <c r="B29" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="28">
+        <v>5</v>
+      </c>
       <c r="G29" s="27"/>
       <c r="H29" s="21"/>
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="26"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="28"/>
+      <c r="B30" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="28">
+        <v>5</v>
+      </c>
       <c r="G30" s="27"/>
       <c r="H30" s="21"/>
       <c r="I30" s="14"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="26"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="28"/>
+      <c r="B31" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="28">
+        <v>5</v>
+      </c>
       <c r="G31" s="27"/>
       <c r="H31" s="21"/>
       <c r="I31" s="14"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="26"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="28"/>
+      <c r="B32" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="28">
+        <v>5</v>
+      </c>
       <c r="G32" s="27"/>
       <c r="H32" s="21"/>
       <c r="I32" s="14"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="26"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="28"/>
+      <c r="B33" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="28">
+        <v>5</v>
+      </c>
       <c r="G33" s="27"/>
       <c r="H33" s="21"/>
-      <c r="I33" s="14"/>
+      <c r="I33" s="14" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="26"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="28"/>
+      <c r="B34" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="28">
+        <v>5</v>
+      </c>
       <c r="G34" s="27"/>
       <c r="H34" s="21"/>
       <c r="I34" s="14"/>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="26"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="28"/>
+      <c r="B35" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="28">
+        <v>5</v>
+      </c>
       <c r="G35" s="27"/>
       <c r="H35" s="21"/>
       <c r="I35" s="14"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="26"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="28"/>
+      <c r="B36" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="28">
+        <v>5</v>
+      </c>
       <c r="G36" s="27"/>
       <c r="H36" s="21"/>
       <c r="I36" s="14"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="26"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="28"/>
+      <c r="B37" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="28">
+        <v>5</v>
+      </c>
       <c r="G37" s="27"/>
       <c r="H37" s="21"/>
       <c r="I37" s="14"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="26"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="28"/>
+      <c r="B38" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="28">
+        <v>5</v>
+      </c>
       <c r="G38" s="27"/>
       <c r="H38" s="21"/>
       <c r="I38" s="14"/>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="26"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="28"/>
+      <c r="B39" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="28">
+        <v>5</v>
+      </c>
       <c r="G39" s="27"/>
       <c r="H39" s="21"/>
       <c r="I39" s="14"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="26"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="28"/>
+      <c r="B40" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="28">
+        <v>5</v>
+      </c>
       <c r="G40" s="27"/>
       <c r="H40" s="21"/>
       <c r="I40" s="14"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="26"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="28"/>
+      <c r="B41" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="28">
+        <v>5</v>
+      </c>
       <c r="G41" s="27"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="14"/>
+      <c r="I41" s="14" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="26"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="28"/>
+      <c r="B42" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="28">
+        <v>5</v>
+      </c>
       <c r="G42" s="27"/>
       <c r="H42" s="21"/>
-      <c r="I42" s="14"/>
+      <c r="I42" s="14" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="26"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="23"/>
+      <c r="B43" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="23">
+        <v>5</v>
+      </c>
       <c r="G43" s="22"/>
       <c r="H43" s="21"/>
-      <c r="I43" s="14"/>
+      <c r="I43" s="14" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="26"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="28"/>
+      <c r="B44" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="28">
+        <v>5</v>
+      </c>
       <c r="G44" s="27"/>
       <c r="H44" s="21"/>
-      <c r="I44" s="14"/>
+      <c r="I44" s="14" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="45" spans="2:9">
-      <c r="B45" s="26"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="28"/>
+      <c r="B45" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="28">
+        <v>5</v>
+      </c>
       <c r="G45" s="27"/>
       <c r="H45" s="21"/>
-      <c r="I45" s="14"/>
+      <c r="I45" s="14" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="26"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="28"/>
+      <c r="B46" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="28">
+        <v>5</v>
+      </c>
       <c r="G46" s="27"/>
       <c r="H46" s="21"/>
-      <c r="I46" s="14"/>
+      <c r="I46" s="14" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="26"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="23"/>
+      <c r="B47" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="23">
+        <v>5</v>
+      </c>
       <c r="G47" s="22"/>
       <c r="H47" s="21"/>
-      <c r="I47" s="14"/>
+      <c r="I47" s="14" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="26"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="23"/>
+      <c r="B48" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="23">
+        <v>5</v>
+      </c>
       <c r="G48" s="22"/>
       <c r="H48" s="21"/>
-      <c r="I48" s="14"/>
+      <c r="I48" s="14" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="49" spans="2:10">
-      <c r="B49" s="26"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="23"/>
+      <c r="B49" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="23">
+        <v>5</v>
+      </c>
       <c r="G49" s="22"/>
       <c r="H49" s="21"/>
-      <c r="I49" s="14"/>
+      <c r="I49" s="14" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="50" spans="2:10" s="13" customFormat="1">
-      <c r="B50" s="26"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="23"/>
+      <c r="B50" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="23">
+        <v>5</v>
+      </c>
       <c r="G50" s="22"/>
       <c r="H50" s="21"/>
-      <c r="I50" s="14"/>
+      <c r="I50" s="14" t="s">
+        <v>18</v>
+      </c>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="2:10">
-      <c r="B51" s="26"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="23"/>
+      <c r="B51" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="23">
+        <v>5</v>
+      </c>
       <c r="G51" s="22"/>
       <c r="H51" s="21"/>
-      <c r="I51" s="14"/>
+      <c r="I51" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="J51" s="13"/>
     </row>
     <row r="52" spans="2:10">
-      <c r="B52" s="26"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="23"/>
+      <c r="B52" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="23">
+        <v>5</v>
+      </c>
       <c r="G52" s="22"/>
       <c r="H52" s="21"/>
-      <c r="I52" s="14"/>
+      <c r="I52" s="14" t="s">
+        <v>15</v>
+      </c>
       <c r="J52" s="13"/>
     </row>
     <row r="53" spans="2:10">
-      <c r="B53" s="26"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="23"/>
+      <c r="B53" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="23">
+        <v>5</v>
+      </c>
       <c r="G53" s="22"/>
       <c r="H53" s="21"/>
-      <c r="I53" s="14"/>
+      <c r="I53" s="14" t="s">
+        <v>14</v>
+      </c>
       <c r="J53" s="13"/>
     </row>
     <row r="54" spans="2:10">
-      <c r="B54" s="26"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="23"/>
+      <c r="B54" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="23">
+        <v>5</v>
+      </c>
       <c r="G54" s="22"/>
       <c r="H54" s="21"/>
-      <c r="I54" s="14"/>
+      <c r="I54" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="J54" s="13"/>
     </row>
     <row r="55" spans="2:10">
-      <c r="B55" s="26"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="23"/>
+      <c r="B55" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="23">
+        <v>5</v>
+      </c>
       <c r="G55" s="22"/>
       <c r="H55" s="21"/>
-      <c r="I55" s="14"/>
+      <c r="I55" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="J55" s="13"/>
     </row>
     <row r="56" spans="2:10">
-      <c r="B56" s="26"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="23"/>
+      <c r="B56" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="23">
+        <v>5</v>
+      </c>
       <c r="G56" s="22"/>
       <c r="H56" s="21"/>
-      <c r="I56" s="14"/>
+      <c r="I56" s="14" t="s">
+        <v>11</v>
+      </c>
       <c r="J56" s="13"/>
     </row>
     <row r="57" spans="2:10">
-      <c r="B57" s="26"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="23"/>
+      <c r="B57" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="23">
+        <v>5</v>
+      </c>
       <c r="G57" s="22"/>
       <c r="H57" s="21"/>
-      <c r="I57" s="14"/>
+      <c r="I57" s="14" t="s">
+        <v>9</v>
+      </c>
       <c r="J57" s="13"/>
     </row>
     <row r="58" spans="2:10">
-      <c r="B58" s="20"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="17"/>
+      <c r="B58" s="20">
+        <v>43040</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="17">
+        <v>5</v>
+      </c>
       <c r="G58" s="16"/>
       <c r="H58" s="15"/>
-      <c r="I58" s="14"/>
+      <c r="I58" s="14" t="s">
+        <v>5</v>
+      </c>
       <c r="J58" s="13"/>
     </row>
     <row r="59" spans="2:10">
       <c r="B59" s="12"/>
       <c r="C59" s="11"/>
       <c r="D59" s="6"/>
-      <c r="E59" s="11" t="s">
-        <v>74</v>
-      </c>
+      <c r="E59" s="11"/>
       <c r="F59" s="10"/>
       <c r="G59" s="9"/>
       <c r="H59" s="8"/>
@@ -5181,1267 +6714,384 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>"社員,派遣"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="81" orientation="portrait" verticalDpi="4294967293" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>入力規則!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>E4:E58</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:J117"/>
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12" style="4" customWidth="1"/>
-    <col min="4" max="4" width="19.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="7.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="41.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="B1" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="36"/>
-      <c r="B2" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="21.75" customHeight="1">
-      <c r="B3" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="B4" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="28">
-        <v>5.12</v>
-      </c>
-      <c r="G4" s="27"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="B5" s="26">
-        <v>43041</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="28">
-        <v>6.03</v>
-      </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="32">
-        <v>3</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="26">
-        <v>43041</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="28">
-        <v>6.03</v>
-      </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="B7" s="26">
-        <v>43044</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="27">
-        <v>4</v>
-      </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="B8" s="26">
-        <v>43045</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="28">
-        <v>6.03</v>
-      </c>
-      <c r="G8" s="27"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="B9" s="26">
-        <v>43054</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="28">
-        <v>5</v>
-      </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10" s="26">
-        <v>43055</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="28">
-        <v>6.03</v>
-      </c>
-      <c r="G10" s="27"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="B11" s="26">
-        <v>43047</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="28">
-        <v>8.2219999999999995</v>
-      </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="B12" s="26">
-        <v>43046</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="28"/>
-      <c r="G12" s="27">
-        <v>5</v>
-      </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" s="26">
-        <v>43062</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="27">
-        <v>1</v>
-      </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" s="26">
-        <v>43045</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="28">
-        <v>8</v>
-      </c>
-      <c r="G14" s="27"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="B15" s="26">
-        <v>43048</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="28">
-        <v>8</v>
-      </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="B16" s="26">
-        <v>43048</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="28">
-        <v>8</v>
-      </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="28">
-        <v>5</v>
-      </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="28">
-        <v>5</v>
-      </c>
-      <c r="G18" s="27"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="28">
-        <v>5</v>
-      </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="28">
-        <v>5</v>
-      </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="28">
-        <v>5</v>
-      </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="28">
-        <v>5</v>
-      </c>
-      <c r="G22" s="27"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="28">
-        <v>5</v>
-      </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="28">
-        <v>5</v>
-      </c>
-      <c r="G24" s="27"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="28">
-        <v>5</v>
-      </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B26" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="28">
-        <v>5</v>
-      </c>
-      <c r="G26" s="27"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="28">
-        <v>5</v>
-      </c>
-      <c r="G27" s="27"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="28">
-        <v>5</v>
-      </c>
-      <c r="G28" s="27"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="28">
-        <v>5</v>
-      </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="14"/>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="28">
-        <v>5</v>
-      </c>
-      <c r="G30" s="27"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="28">
-        <v>5</v>
-      </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="28">
-        <v>5</v>
-      </c>
-      <c r="G32" s="27"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="14"/>
-    </row>
-    <row r="33" spans="2:9">
-      <c r="B33" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="28">
-        <v>5</v>
-      </c>
-      <c r="G33" s="27"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9">
-      <c r="B34" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="28">
-        <v>5</v>
-      </c>
-      <c r="G34" s="27"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="14"/>
-    </row>
-    <row r="35" spans="2:9">
-      <c r="B35" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="28">
-        <v>5</v>
-      </c>
-      <c r="G35" s="27"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="14"/>
-    </row>
-    <row r="36" spans="2:9">
-      <c r="B36" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="28">
-        <v>5</v>
-      </c>
-      <c r="G36" s="27"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="14"/>
-    </row>
-    <row r="37" spans="2:9">
-      <c r="B37" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="28">
-        <v>5</v>
-      </c>
-      <c r="G37" s="27"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="14"/>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="B38" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="28">
-        <v>5</v>
-      </c>
-      <c r="G38" s="27"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="14"/>
-    </row>
-    <row r="39" spans="2:9">
-      <c r="B39" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="28">
-        <v>5</v>
-      </c>
-      <c r="G39" s="27"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="14"/>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="28">
-        <v>5</v>
-      </c>
-      <c r="G40" s="27"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="14"/>
-    </row>
-    <row r="41" spans="2:9">
-      <c r="B41" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E41" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="28">
-        <v>5</v>
-      </c>
-      <c r="G41" s="27"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="28">
-        <v>5</v>
-      </c>
-      <c r="G42" s="27"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9">
-      <c r="B43" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="23">
-        <v>5</v>
-      </c>
-      <c r="G43" s="22"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="28">
-        <v>5</v>
-      </c>
-      <c r="G44" s="27"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9">
-      <c r="B45" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="28">
-        <v>5</v>
-      </c>
-      <c r="G45" s="27"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="28">
-        <v>5</v>
-      </c>
-      <c r="G46" s="27"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9">
-      <c r="B47" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="23">
-        <v>5</v>
-      </c>
-      <c r="G47" s="22"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="23">
-        <v>5</v>
-      </c>
-      <c r="G48" s="22"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="B49" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="23">
-        <v>5</v>
-      </c>
-      <c r="G49" s="22"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" s="13" customFormat="1">
-      <c r="B50" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="23">
-        <v>5</v>
-      </c>
-      <c r="G50" s="22"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="23">
-        <v>5</v>
-      </c>
-      <c r="G51" s="22"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="13"/>
-    </row>
-    <row r="52" spans="2:10">
-      <c r="B52" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E52" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="23">
-        <v>5</v>
-      </c>
-      <c r="G52" s="22"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" s="13"/>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="23">
-        <v>5</v>
-      </c>
-      <c r="G53" s="22"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J53" s="13"/>
-    </row>
-    <row r="54" spans="2:10">
-      <c r="B54" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="23">
-        <v>5</v>
-      </c>
-      <c r="G54" s="22"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="13"/>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="23">
-        <v>5</v>
-      </c>
-      <c r="G55" s="22"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J55" s="13"/>
-    </row>
-    <row r="56" spans="2:10">
-      <c r="B56" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="23">
-        <v>5</v>
-      </c>
-      <c r="G56" s="22"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J56" s="13"/>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="23">
-        <v>5</v>
-      </c>
-      <c r="G57" s="22"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J57" s="13"/>
-    </row>
-    <row r="58" spans="2:10">
-      <c r="B58" s="20">
-        <v>43040</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F58" s="17">
-        <v>5</v>
-      </c>
-      <c r="G58" s="16"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" spans="2:10">
-      <c r="B59" s="12"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F59" s="10"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="7"/>
-    </row>
-    <row r="60" spans="2:10">
-      <c r="B60" s="37"/>
-    </row>
-    <row r="61" spans="2:10" ht="27" customHeight="1"/>
-    <row r="110" spans="2:2">
-      <c r="B110" s="5"/>
-    </row>
-    <row r="111" spans="2:2">
-      <c r="B111" s="5"/>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112" s="6"/>
-    </row>
-    <row r="113" spans="2:2">
-      <c r="B113" s="5"/>
-    </row>
-    <row r="114" spans="2:2">
-      <c r="B114" s="6"/>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="5"/>
-    </row>
-    <row r="116" spans="2:2">
-      <c r="B116" s="6"/>
-    </row>
-    <row r="117" spans="2:2">
-      <c r="B117" s="5"/>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="67.5">
+      <c r="A34" s="39" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="81" orientation="portrait" verticalDpi="4294967293" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/伊藤工数表.xlsx
+++ b/伊藤工数表.xlsx
@@ -4,27 +4,29 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="750" windowWidth="18315" windowHeight="11220" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="780" windowWidth="18315" windowHeight="11190"/>
   </bookViews>
   <sheets>
-    <sheet name="原紙(入力)" sheetId="5" r:id="rId1"/>
-    <sheet name="2017.1" sheetId="9" r:id="rId2"/>
-    <sheet name="2017.2" sheetId="10" r:id="rId3"/>
-    <sheet name="2017.12" sheetId="11" r:id="rId4"/>
-    <sheet name="入力規則" sheetId="14" state="veryHidden" r:id="rId5"/>
+    <sheet name="操作説明" sheetId="17" r:id="rId1"/>
+    <sheet name="コピー用" sheetId="15" r:id="rId2"/>
+    <sheet name="2017.7" sheetId="16" r:id="rId3"/>
+    <sheet name="2017.1" sheetId="9" r:id="rId4"/>
+    <sheet name="2017.2" sheetId="10" r:id="rId5"/>
+    <sheet name="入力規則" sheetId="14" state="veryHidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2017.1'!$B$3:$I$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'2017.12'!$B$3:$I$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2017.2'!$B$3:$I$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'原紙(入力)'!$B$3:$I$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'2017.1'!$B$3:$J$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'2017.2'!$B$3:$J$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2017.7'!$B$3:$J$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">コピー用!$B$3:$J$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">操作説明!$B$3:$J$58</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="180">
   <si>
     <t>end4</t>
     <phoneticPr fontId="1"/>
@@ -120,10 +122,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>A1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>HH16-0047</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -157,18 +155,6 @@
   </si>
   <si>
     <t>HH16-0042</t>
-  </si>
-  <si>
-    <t>DSC-6AB</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HH</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HH16-0041</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>配線手直し</t>
@@ -181,10 +167,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MM-D72C</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>HH</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -334,266 +316,401 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>first1</t>
-  </si>
-  <si>
-    <t>HH16-0047</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
     <t>DSE3-6AV</t>
   </si>
   <si>
-    <t>A2</t>
-  </si>
-  <si>
     <t>DSC-6AB</t>
   </si>
   <si>
-    <t>HH16-0041</t>
-  </si>
-  <si>
-    <t>B0</t>
-  </si>
-  <si>
-    <t>ＩＮＶ</t>
-  </si>
-  <si>
-    <t>INV</t>
-  </si>
-  <si>
-    <t>last</t>
-  </si>
-  <si>
-    <t>check</t>
-  </si>
-  <si>
-    <t>end</t>
-  </si>
-  <si>
-    <t>end2</t>
-  </si>
-  <si>
-    <t>end3</t>
-  </si>
-  <si>
-    <t>end4</t>
-  </si>
-  <si>
-    <t>end5</t>
-  </si>
-  <si>
-    <t>end6</t>
-  </si>
-  <si>
-    <t>ＰＧＳ２－２０／３０ＶＣＷ－４／０</t>
-  </si>
-  <si>
-    <t>ＰＧＳ５－２０／３０ＶＣＰＷ－４／０</t>
-  </si>
-  <si>
-    <t>ＳＰＡＣ－Ｇ２０／３０Ｂ</t>
-  </si>
-  <si>
-    <t>ＳＰＡＣ－Ｇ２０／３０Ｃ</t>
-  </si>
-  <si>
-    <t>ＫＬ－Ｐ</t>
-  </si>
-  <si>
-    <t>ＰＶＳ１０－６ＬＦ－４／０</t>
-  </si>
-  <si>
-    <t>ＲＭＤ２（－Ｆ７）</t>
-  </si>
-  <si>
-    <t>ＭＭ－Ｄ４１（一般向け）</t>
-  </si>
-  <si>
-    <t>ＭＭ－Ｄ４１Ｇ（関電向け）</t>
-  </si>
-  <si>
-    <t>ＭＭ－Ｄ４１　鎖錠装置取付作業</t>
-  </si>
-  <si>
-    <t>ＭＭ－Ｄ４３</t>
-  </si>
-  <si>
-    <t>ＭＭ－Ｄ５１ＢＬ</t>
-  </si>
-  <si>
-    <t>ＭＭ－Ｄ７１Ａ</t>
-  </si>
-  <si>
-    <t>ＭＭ－Ｄ７２Ａ</t>
-  </si>
-  <si>
-    <t>ＭＭ－Ｄ７２Ｂ</t>
-  </si>
-  <si>
-    <t>ＭＭ－Ｄ７２Ｃ</t>
-  </si>
-  <si>
-    <t>ＲＨ－ＤＬ</t>
-  </si>
-  <si>
-    <t>ＲＨ－ＤＬ（関電仕様）</t>
-  </si>
-  <si>
-    <t>ＲＨ－ＤＬ（前橋向け）</t>
-  </si>
-  <si>
-    <t>ＲＨ－ＤＮ</t>
-  </si>
-  <si>
-    <t>ＲＨ－Ｄ</t>
-  </si>
-  <si>
-    <t>ＲＨ－ＥＬ</t>
-  </si>
-  <si>
-    <t>ＲＨ－Ｆ(Ｌ)</t>
-  </si>
-  <si>
-    <t>ＲＨ－ＨＬ１</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－６Ａ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－６ＡＢ</t>
-  </si>
-  <si>
-    <t>地上設置型変圧器箱</t>
-  </si>
-  <si>
-    <t>ＰＶＳ２０－６ＶＦ－４／０</t>
-  </si>
-  <si>
-    <t>ＭＫ－７</t>
-  </si>
-  <si>
     <t>工事車</t>
   </si>
   <si>
     <t>外箱</t>
   </si>
   <si>
-    <t>バッテリー組立</t>
-  </si>
-  <si>
-    <t>メガセーフ１バンク分
-（ｺﾝﾃﾞﾝｻ60set、INV18set）</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－６Ｂ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－６ＡＤ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－６ＢＤ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－６ＢＢ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－６ＣＤ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－１０ＢＢ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－１０ＢＤ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－２１ＡＢ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－２１ＡＤ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－２１ＡＤＧ（負荷側接地）</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－２１ＡＤＧ（電源側接地）</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－２１ＡＤＳ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－３０ＢＤ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－３１ＡＤ</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－３１ＡＤＧ（電源側接地）</t>
-  </si>
-  <si>
-    <t>ＤＳＣ－３１ＡＤＳ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－６ＡＶ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－６ＡＶ－４Ｌ／Ｒ２（２極断路器）</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－６ＡＤＧ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ２－６ＡＶ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ３－６ＡＶ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－８Ｇ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－２０ＡＶ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－２０ＡＶＧ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－２０ＡＶＧＳ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－２１ＡＤ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－３０ＡＶ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－３０ＡＶＧ</t>
-  </si>
-  <si>
-    <t>ＤＳＥ－３０ＡＶＧＳ</t>
-  </si>
-  <si>
-    <t>ＧＤＳＥ－８Ｇ</t>
-  </si>
-  <si>
-    <t>ＬＤＳ－２０ＡＶ</t>
-  </si>
-  <si>
-    <t>ＬＤＳ－３０ＡＶ</t>
-  </si>
-  <si>
-    <t>ＮＲＤＳ－３０ＦＧＳ</t>
-  </si>
-  <si>
-    <t>首都高用</t>
+    <t>KL-P</t>
+  </si>
+  <si>
+    <t>MM-D41(一般向け)</t>
+  </si>
+  <si>
+    <t>MM-D43</t>
+  </si>
+  <si>
+    <t>MM-D51BL</t>
+  </si>
+  <si>
+    <t>MM-D72A</t>
+  </si>
+  <si>
+    <t>MM-D72B</t>
+  </si>
+  <si>
+    <t>RH-DN</t>
+  </si>
+  <si>
+    <t>RH-D</t>
+  </si>
+  <si>
+    <t>RH-EL</t>
+  </si>
+  <si>
+    <t>RH-HL1</t>
+  </si>
+  <si>
+    <t>DSC-6A</t>
+  </si>
+  <si>
+    <t>MK-7</t>
+  </si>
+  <si>
+    <t>DSC-6B</t>
+  </si>
+  <si>
+    <t>DSC-6AD</t>
+  </si>
+  <si>
+    <t>DSC-6BD</t>
+  </si>
+  <si>
+    <t>DSC-6BB</t>
+  </si>
+  <si>
+    <t>DSC-6CD</t>
+  </si>
+  <si>
+    <t>DSC-10BB</t>
+  </si>
+  <si>
+    <t>DSC-10BD</t>
+  </si>
+  <si>
+    <t>DSC-21AB</t>
+  </si>
+  <si>
+    <t>DSC-21AD</t>
+  </si>
+  <si>
+    <t>DSC-21ADS</t>
+  </si>
+  <si>
+    <t>DSC-30BD</t>
+  </si>
+  <si>
+    <t>DSC-31AD</t>
+  </si>
+  <si>
+    <t>DSC-31ADS</t>
+  </si>
+  <si>
+    <t>DSE-6AV</t>
+  </si>
+  <si>
+    <t>DSE-8G</t>
+  </si>
+  <si>
+    <t>DSE-20AV</t>
+  </si>
+  <si>
+    <t>DSE-20AVG</t>
+  </si>
+  <si>
+    <t>DSE-20AVGS</t>
+  </si>
+  <si>
+    <t>DSE-21AD</t>
+  </si>
+  <si>
+    <t>DSE-30AV</t>
+  </si>
+  <si>
+    <t>DSE-30AVG</t>
+  </si>
+  <si>
+    <t>DSE-30AVGS</t>
+  </si>
+  <si>
+    <t>GDSE-8G</t>
+  </si>
+  <si>
+    <t>LDS-20AV</t>
+  </si>
+  <si>
+    <t>LDS-30AV</t>
+  </si>
+  <si>
+    <t>NRDS-30FGS</t>
   </si>
   <si>
     <t>派遣</t>
   </si>
   <si>
-    <t>aa</t>
+    <t>ＰＰ１６－０５６１</t>
+  </si>
+  <si>
+    <t>ＢＥ</t>
+  </si>
+  <si>
+    <t>工具管理</t>
+  </si>
+  <si>
+    <t>ＨＨ１７－００２８</t>
+  </si>
+  <si>
+    <t>ＨＨ</t>
+  </si>
+  <si>
+    <t>出張</t>
+  </si>
+  <si>
+    <t>９９ＸＰ１７－１００３</t>
+  </si>
+  <si>
+    <t>Ｋ９</t>
+  </si>
+  <si>
+    <t>１１ＸＨ１６－１１６７</t>
+  </si>
+  <si>
+    <t>ＢＡ</t>
+  </si>
+  <si>
+    <t>５３ＨＨ１７－３００１</t>
+  </si>
+  <si>
+    <t>ＨＨ１７－００１８</t>
+  </si>
+  <si>
+    <t>１１ＸＨ１６－１１７２</t>
+  </si>
+  <si>
+    <t>Ｂ１</t>
+  </si>
+  <si>
+    <t>ＢＧ</t>
+  </si>
+  <si>
+    <t>ＰＨ１５－０２３３</t>
+  </si>
+  <si>
+    <t>Ｂ０</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>雑務</t>
+    <rPh sb="0" eb="2">
+      <t>ザツム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>工具管理</t>
+    <rPh sb="0" eb="2">
+      <t>コウグ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ＰＰ１６－０５６１</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出張</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ＨＨ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出張</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>準備</t>
+    <rPh sb="0" eb="2">
+      <t>ジュンビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MM-D73C</t>
+  </si>
+  <si>
+    <t>99XP16-1029</t>
+  </si>
+  <si>
+    <t>K4</t>
+  </si>
+  <si>
+    <t>DSE-7ADG</t>
+  </si>
+  <si>
+    <t>MM-D42(一般向け)</t>
+  </si>
+  <si>
+    <t>火元</t>
+    <rPh sb="0" eb="2">
+      <t>ヒモト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PGS2-30VCW</t>
+  </si>
+  <si>
+    <t>PGS5-20VCPW</t>
+  </si>
+  <si>
+    <t>PGS5-30VCPW</t>
+  </si>
+  <si>
+    <t>SPAC-G20B</t>
+  </si>
+  <si>
+    <t>SPAC-G30B</t>
+  </si>
+  <si>
+    <t>SPAC-G20C</t>
+  </si>
+  <si>
+    <t>SPAC-G30C</t>
+  </si>
+  <si>
+    <t>PVS10-6LF</t>
+  </si>
+  <si>
+    <t>PVS20-6VF</t>
+  </si>
+  <si>
+    <t>H変台</t>
+  </si>
+  <si>
+    <t>ﾊﾞｯﾃﾘｰ</t>
+  </si>
+  <si>
+    <t>INV単品</t>
+  </si>
+  <si>
+    <t>INVﾕﾆｯﾄ</t>
+  </si>
+  <si>
+    <t>ｺﾝﾃﾞﾝｻﾕﾆｯﾄ</t>
+  </si>
+  <si>
+    <t>工事車点検</t>
+  </si>
+  <si>
+    <t>RMD2</t>
+  </si>
+  <si>
+    <t>MM-D41</t>
+  </si>
+  <si>
+    <t>MM-D41G</t>
+  </si>
+  <si>
+    <t>RH-DL(一般)</t>
+  </si>
+  <si>
+    <t>RH-DL(関電)</t>
+  </si>
+  <si>
+    <t>RH-DL(前橋)</t>
+  </si>
+  <si>
+    <t>RH-F</t>
+  </si>
+  <si>
+    <t>DSC-21ADG</t>
+  </si>
+  <si>
+    <t>DSC-31ADG</t>
+  </si>
+  <si>
+    <t>DSE-6AV(2極)</t>
+  </si>
+  <si>
+    <t>首都高用接地機構部</t>
+  </si>
+  <si>
+    <t>雑務</t>
+    <rPh sb="0" eb="2">
+      <t>ザツム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>工具管理</t>
+    <rPh sb="0" eb="2">
+      <t>コウグ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火元</t>
+    <rPh sb="0" eb="2">
+      <t>ヒモト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火元</t>
+    <rPh sb="0" eb="2">
+      <t>ヒモト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出張</t>
+    <rPh sb="0" eb="2">
+      <t>シュッチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PGS2-20VCW</t>
+  </si>
+  <si>
+    <t>京神倉庫</t>
+    <rPh sb="0" eb="2">
+      <t>ケイシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電試</t>
+    <rPh sb="0" eb="1">
+      <t>デン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>連系装置</t>
+    <rPh sb="0" eb="2">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員</t>
   </si>
 </sst>
 </file>
@@ -601,7 +718,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
+    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0_);[Red]\(&quot;¥&quot;#,##0\)"/>
     <numFmt numFmtId="177" formatCode="m/d;@"/>
   </numFmts>
   <fonts count="8">
@@ -761,7 +878,7 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -861,9 +978,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="通貨 2" xfId="2"/>
@@ -885,7 +999,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -900,7 +1014,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6172200" y="10353675"/>
+          <a:off x="10077450" y="10467975"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -972,7 +1086,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2057400" y="10363200"/>
+          <a:off x="1609725" y="10477500"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1029,7 +1143,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1044,7 +1158,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6172200" y="10353675"/>
+          <a:off x="10077450" y="10467975"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1101,7 +1215,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1116,7 +1230,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6172200" y="10353675"/>
+          <a:off x="10077450" y="10467975"/>
           <a:ext cx="19050" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1166,7 +1280,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2057400" y="10363200"/>
+          <a:off x="1609725" y="10477500"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1223,7 +1337,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1238,7 +1352,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6172200" y="10353675"/>
+          <a:off x="10077450" y="10467975"/>
           <a:ext cx="108812" cy="201850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1293,6 +1407,508 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>563217</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4228572" cy="1380952"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5173317" y="2499277"/>
+          <a:ext cx="4228572" cy="1380952"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571498</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>2642152</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト ボックス 8"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5181598" y="1813477"/>
+          <a:ext cx="4394754" cy="691598"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0"/>
+            <a:t>製品名はドロップダウンリストから選択して入力できます。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0"/>
+            <a:t>また、下のような警告が出ますが、直接入力することも可能です。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0"/>
+            <a:t>下のような警告が出た場合は　はい</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0"/>
+            <a:t>Ｙ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0"/>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0"/>
+            <a:t>　を選択すれば入力が可能です。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1258959</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>91110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571498</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>169793</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線矢印コネクタ 9"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="4430784" y="1053135"/>
+          <a:ext cx="750814" cy="1107383"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>414128</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>66260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1391477</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>157368</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="テキスト ボックス 10"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="652253" y="1714085"/>
+          <a:ext cx="3911049" cy="948358"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>工数と群番はデータが入力されている場合、作業工数</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>報告表に記載されます。逆に、工数と群番がデータ入力されていなければ、雑務として処理され、集計の部分にのみ反映</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>されます。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>472108</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>115957</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>923509</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>66260</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線矢印コネクタ 11"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="1243633" y="735082"/>
+          <a:ext cx="1365801" cy="979003"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>637760</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>49696</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>923509</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>66260</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線矢印コネクタ 12"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2323685" y="668821"/>
+          <a:ext cx="285749" cy="1045264"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>124239</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>49696</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>339586</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>8283</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="テキスト ボックス 13"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="124239" y="2932044"/>
+          <a:ext cx="3379304" cy="654326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>社員か派遣かを選ぶドロップダウンリストが出ます。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>そのどちらかを選択してください。社員か派遣で、</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>作業工数報告表での位置が変わります。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>124239</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>165654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>140805</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>28990</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線矢印コネクタ 14"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="124239" y="339589"/>
+          <a:ext cx="256762" cy="2919618"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+        <a:effectLst>
+          <a:glow rad="63500">
+            <a:schemeClr val="accent2">
+              <a:satMod val="175000"/>
+              <a:alpha val="40000"/>
+            </a:schemeClr>
+          </a:glow>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1300,7 +1916,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1444,7 +2060,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1516,7 +2132,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1638,7 +2254,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1715,7 +2331,422 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="108812" cy="201850"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Text Box 1"/>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8549640" y="10239375"/>
+          <a:ext cx="108812" cy="201850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="18288" tIns="18288" rIns="0" bIns="0" anchor="t" upright="1">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>H</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="108812" cy="201850"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Text Box 2"/>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1516380" y="10248900"/>
+          <a:ext cx="108812" cy="201850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="18288" tIns="18288" rIns="0" bIns="0" anchor="t" upright="1">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>H</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="108812" cy="201850"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Text Box 3"/>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8549640" y="10239375"/>
+          <a:ext cx="108812" cy="201850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="18288" tIns="18288" rIns="0" bIns="0" anchor="t" upright="1">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>H</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="19050" cy="171450"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Text Box 4"/>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8549640" y="10239375"/>
+          <a:ext cx="19050" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="108812" cy="201850"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Text Box 5"/>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1516380" y="10248900"/>
+          <a:ext cx="108812" cy="201850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="18288" tIns="18288" rIns="0" bIns="0" anchor="t" upright="1">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>H</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="108812" cy="201850"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Text Box 6"/>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8549640" y="10239375"/>
+          <a:ext cx="108812" cy="201850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="18288" tIns="18288" rIns="0" bIns="0" anchor="t" upright="1">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>H</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1859,7 +2890,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1931,7 +2962,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -2053,7 +3084,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -2126,11 +3157,11 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -2274,7 +3305,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -2346,7 +3377,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -2468,7 +3499,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -2828,8 +3859,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J117"/>
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
@@ -2837,642 +3868,741 @@
     <col min="3" max="3" width="12" style="4" customWidth="1"/>
     <col min="4" max="4" width="19.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="7.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="41.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="6" max="8" width="7.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="41.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="36"/>
       <c r="B2" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="21.75" customHeight="1">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="21.75" customHeight="1">
       <c r="B3" s="34" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>143</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>41</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4" s="26"/>
       <c r="C4" s="24"/>
       <c r="D4" s="25"/>
       <c r="E4" s="24"/>
       <c r="F4" s="28"/>
       <c r="G4" s="27"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="33"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="H4" s="27"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="33"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5" s="26"/>
       <c r="C5" s="24"/>
       <c r="D5" s="25"/>
       <c r="E5" s="24"/>
       <c r="F5" s="28"/>
       <c r="G5" s="27"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="H5" s="27"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="26"/>
       <c r="C6" s="24"/>
       <c r="D6" s="31"/>
       <c r="E6" s="24"/>
       <c r="F6" s="28"/>
       <c r="G6" s="27"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="H6" s="27"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7" s="26"/>
       <c r="C7" s="24"/>
       <c r="D7" s="25"/>
       <c r="E7" s="24"/>
       <c r="F7" s="28"/>
       <c r="G7" s="27"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="H7" s="27"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" s="26"/>
       <c r="C8" s="24"/>
       <c r="D8" s="25"/>
       <c r="E8" s="24"/>
       <c r="F8" s="28"/>
       <c r="G8" s="27"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="H8" s="27"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="26"/>
       <c r="C9" s="24"/>
       <c r="D9" s="25"/>
       <c r="E9" s="24"/>
       <c r="F9" s="28"/>
       <c r="G9" s="27"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="H9" s="27"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10" s="26"/>
       <c r="C10" s="24"/>
       <c r="D10" s="30"/>
       <c r="E10" s="24"/>
       <c r="F10" s="28"/>
       <c r="G10" s="27"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="H10" s="27"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11" s="26"/>
       <c r="C11" s="24"/>
       <c r="D11" s="25"/>
       <c r="E11" s="24"/>
       <c r="F11" s="28"/>
       <c r="G11" s="27"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="H11" s="27"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" s="26"/>
       <c r="C12" s="24"/>
       <c r="D12" s="25"/>
       <c r="E12" s="24"/>
       <c r="F12" s="28"/>
       <c r="G12" s="27"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="H12" s="27"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" s="26"/>
       <c r="C13" s="24"/>
       <c r="D13" s="25"/>
       <c r="E13" s="24"/>
       <c r="F13" s="28"/>
       <c r="G13" s="27"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="H13" s="27"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="26"/>
       <c r="C14" s="24"/>
       <c r="D14" s="25"/>
       <c r="E14" s="24"/>
       <c r="F14" s="28"/>
       <c r="G14" s="27"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="H14" s="27"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15" s="26"/>
       <c r="C15" s="24"/>
       <c r="D15" s="25"/>
       <c r="E15" s="24"/>
       <c r="F15" s="28"/>
       <c r="G15" s="27"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="14"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="H15" s="27"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16" s="26"/>
       <c r="C16" s="24"/>
       <c r="D16" s="25"/>
       <c r="E16" s="24"/>
       <c r="F16" s="28"/>
       <c r="G16" s="27"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="2:9">
+      <c r="H16" s="27"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17" s="26"/>
       <c r="C17" s="24"/>
       <c r="D17" s="25"/>
       <c r="E17" s="24"/>
       <c r="F17" s="28"/>
       <c r="G17" s="27"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="2:9">
+      <c r="H17" s="27"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18" s="26"/>
       <c r="C18" s="24"/>
       <c r="D18" s="25"/>
       <c r="E18" s="24"/>
       <c r="F18" s="28"/>
       <c r="G18" s="27"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="2:9">
+      <c r="H18" s="27"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19" s="26"/>
       <c r="C19" s="24"/>
       <c r="D19" s="25"/>
       <c r="E19" s="24"/>
       <c r="F19" s="28"/>
       <c r="G19" s="27"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="2:9">
+      <c r="H19" s="27"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20" s="26"/>
       <c r="C20" s="24"/>
       <c r="D20" s="25"/>
       <c r="E20" s="24"/>
       <c r="F20" s="28"/>
       <c r="G20" s="27"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="2:9">
+      <c r="H20" s="27"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21" s="26"/>
       <c r="C21" s="24"/>
       <c r="D21" s="25"/>
       <c r="E21" s="24"/>
       <c r="F21" s="28"/>
       <c r="G21" s="27"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="2:9">
+      <c r="H21" s="27"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="2:10">
       <c r="B22" s="26"/>
       <c r="C22" s="24"/>
       <c r="D22" s="25"/>
       <c r="E22" s="24"/>
       <c r="F22" s="28"/>
       <c r="G22" s="27"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="2:9">
+      <c r="H22" s="27"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="2:10">
       <c r="B23" s="26"/>
       <c r="C23" s="24"/>
       <c r="D23" s="25"/>
       <c r="E23" s="24"/>
       <c r="F23" s="28"/>
       <c r="G23" s="27"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="2:9">
+      <c r="H23" s="27"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="2:10">
       <c r="B24" s="26"/>
       <c r="C24" s="24"/>
       <c r="D24" s="25"/>
       <c r="E24" s="24"/>
       <c r="F24" s="28"/>
       <c r="G24" s="27"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" spans="2:9">
+      <c r="H24" s="27"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="2:10">
       <c r="B25" s="26"/>
       <c r="C25" s="24"/>
       <c r="D25" s="25"/>
       <c r="E25" s="24"/>
       <c r="F25" s="28"/>
       <c r="G25" s="27"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="2:9" ht="14.25" customHeight="1">
+      <c r="H25" s="27"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="2:10" ht="14.25" customHeight="1">
       <c r="B26" s="26"/>
       <c r="C26" s="24"/>
       <c r="D26" s="25"/>
       <c r="E26" s="24"/>
       <c r="F26" s="28"/>
       <c r="G26" s="27"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" spans="2:9">
+      <c r="H26" s="27"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="2:10">
       <c r="B27" s="26"/>
       <c r="C27" s="24"/>
       <c r="D27" s="25"/>
       <c r="E27" s="24"/>
       <c r="F27" s="28"/>
       <c r="G27" s="27"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" spans="2:9">
+      <c r="H27" s="27"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="2:10">
       <c r="B28" s="26"/>
       <c r="C28" s="24"/>
       <c r="D28" s="25"/>
       <c r="E28" s="24"/>
       <c r="F28" s="28"/>
       <c r="G28" s="27"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" spans="2:9">
+      <c r="H28" s="27"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="2:10">
       <c r="B29" s="26"/>
       <c r="C29" s="24"/>
       <c r="D29" s="25"/>
       <c r="E29" s="24"/>
       <c r="F29" s="28"/>
       <c r="G29" s="27"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="14"/>
-    </row>
-    <row r="30" spans="2:9">
+      <c r="H29" s="27"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="2:10">
       <c r="B30" s="26"/>
       <c r="C30" s="24"/>
       <c r="D30" s="25"/>
       <c r="E30" s="24"/>
       <c r="F30" s="28"/>
       <c r="G30" s="27"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" spans="2:9">
+      <c r="H30" s="27"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="2:10">
       <c r="B31" s="26"/>
       <c r="C31" s="24"/>
       <c r="D31" s="25"/>
       <c r="E31" s="24"/>
       <c r="F31" s="28"/>
       <c r="G31" s="27"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="2:9">
+      <c r="H31" s="27"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="2:10">
       <c r="B32" s="26"/>
       <c r="C32" s="24"/>
       <c r="D32" s="25"/>
       <c r="E32" s="24"/>
       <c r="F32" s="28"/>
       <c r="G32" s="27"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="14"/>
-    </row>
-    <row r="33" spans="2:9">
+      <c r="H32" s="27"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="2:10">
       <c r="B33" s="26"/>
       <c r="C33" s="24"/>
       <c r="D33" s="25"/>
       <c r="E33" s="24"/>
       <c r="F33" s="28"/>
       <c r="G33" s="27"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="14"/>
-    </row>
-    <row r="34" spans="2:9">
+      <c r="H33" s="27"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34" s="26"/>
       <c r="C34" s="24"/>
       <c r="D34" s="25"/>
       <c r="E34" s="24"/>
       <c r="F34" s="28"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="14"/>
-    </row>
-    <row r="35" spans="2:9">
+      <c r="H34" s="27"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="2:10">
       <c r="B35" s="26"/>
       <c r="C35" s="24"/>
       <c r="D35" s="25"/>
       <c r="E35" s="24"/>
       <c r="F35" s="28"/>
       <c r="G35" s="27"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="14"/>
-    </row>
-    <row r="36" spans="2:9">
+      <c r="H35" s="27"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36" s="26"/>
       <c r="C36" s="24"/>
       <c r="D36" s="25"/>
       <c r="E36" s="24"/>
       <c r="F36" s="28"/>
       <c r="G36" s="27"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="14"/>
-    </row>
-    <row r="37" spans="2:9">
+      <c r="H36" s="27"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="2:10">
       <c r="B37" s="26"/>
       <c r="C37" s="24"/>
       <c r="D37" s="25"/>
       <c r="E37" s="24"/>
       <c r="F37" s="28"/>
       <c r="G37" s="27"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="14"/>
-    </row>
-    <row r="38" spans="2:9">
+      <c r="H37" s="27"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="2:10">
       <c r="B38" s="26"/>
       <c r="C38" s="24"/>
       <c r="D38" s="25"/>
       <c r="E38" s="24"/>
       <c r="F38" s="28"/>
       <c r="G38" s="27"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="14"/>
-    </row>
-    <row r="39" spans="2:9">
+      <c r="H38" s="27"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="2:10">
       <c r="B39" s="26"/>
       <c r="C39" s="24"/>
       <c r="D39" s="25"/>
       <c r="E39" s="24"/>
       <c r="F39" s="28"/>
       <c r="G39" s="27"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="14"/>
-    </row>
-    <row r="40" spans="2:9">
+      <c r="H39" s="27"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="2:10">
       <c r="B40" s="26"/>
       <c r="C40" s="24"/>
       <c r="D40" s="25"/>
       <c r="E40" s="24"/>
       <c r="F40" s="28"/>
       <c r="G40" s="27"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="14"/>
-    </row>
-    <row r="41" spans="2:9">
+      <c r="H40" s="27"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="2:10">
       <c r="B41" s="26"/>
       <c r="C41" s="24"/>
       <c r="D41" s="25"/>
       <c r="E41" s="24"/>
       <c r="F41" s="28"/>
       <c r="G41" s="27"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="14"/>
-    </row>
-    <row r="42" spans="2:9">
+      <c r="H41" s="27"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="2:10">
       <c r="B42" s="26"/>
       <c r="C42" s="24"/>
       <c r="D42" s="29"/>
       <c r="E42" s="24"/>
       <c r="F42" s="28"/>
       <c r="G42" s="27"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="14"/>
-    </row>
-    <row r="43" spans="2:9">
+      <c r="H42" s="27"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="2:10">
       <c r="B43" s="26"/>
       <c r="C43" s="24"/>
       <c r="D43" s="25"/>
       <c r="E43" s="24"/>
       <c r="F43" s="23"/>
       <c r="G43" s="22"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="14"/>
-    </row>
-    <row r="44" spans="2:9">
+      <c r="H43" s="22"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="14"/>
+    </row>
+    <row r="44" spans="2:10">
       <c r="B44" s="26"/>
       <c r="C44" s="24"/>
       <c r="D44" s="25"/>
       <c r="E44" s="24"/>
       <c r="F44" s="28"/>
       <c r="G44" s="27"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="14"/>
-    </row>
-    <row r="45" spans="2:9">
+      <c r="H44" s="27"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="2:10">
       <c r="B45" s="26"/>
       <c r="C45" s="24"/>
       <c r="D45" s="25"/>
       <c r="E45" s="24"/>
       <c r="F45" s="28"/>
       <c r="G45" s="27"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="14"/>
-    </row>
-    <row r="46" spans="2:9">
+      <c r="H45" s="27"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="2:10">
       <c r="B46" s="26"/>
       <c r="C46" s="24"/>
       <c r="D46" s="25"/>
       <c r="E46" s="24"/>
       <c r="F46" s="28"/>
       <c r="G46" s="27"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="14"/>
-    </row>
-    <row r="47" spans="2:9">
+      <c r="H46" s="27"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="2:10">
       <c r="B47" s="26"/>
       <c r="C47" s="24"/>
       <c r="D47" s="25"/>
       <c r="E47" s="24"/>
       <c r="F47" s="23"/>
       <c r="G47" s="22"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="14"/>
-    </row>
-    <row r="48" spans="2:9">
+      <c r="H47" s="22"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="2:10">
       <c r="B48" s="26"/>
       <c r="C48" s="24"/>
       <c r="D48" s="25"/>
       <c r="E48" s="24"/>
       <c r="F48" s="23"/>
       <c r="G48" s="22"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="14"/>
-    </row>
-    <row r="49" spans="2:10">
+      <c r="H48" s="22"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="2:11">
       <c r="B49" s="26"/>
       <c r="C49" s="24"/>
       <c r="D49" s="25"/>
       <c r="E49" s="24"/>
       <c r="F49" s="23"/>
       <c r="G49" s="22"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="14"/>
-    </row>
-    <row r="50" spans="2:10" s="13" customFormat="1">
+      <c r="H49" s="22"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="2:11" s="13" customFormat="1">
       <c r="B50" s="26"/>
       <c r="C50" s="24"/>
       <c r="D50" s="25"/>
       <c r="E50" s="24"/>
       <c r="F50" s="23"/>
       <c r="G50" s="22"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="2:10">
+      <c r="H50" s="22"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" spans="2:11">
       <c r="B51" s="26"/>
       <c r="C51" s="24"/>
       <c r="D51" s="25"/>
       <c r="E51" s="24"/>
       <c r="F51" s="23"/>
       <c r="G51" s="22"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="13"/>
-    </row>
-    <row r="52" spans="2:10">
+      <c r="H51" s="22"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" spans="2:11">
       <c r="B52" s="26"/>
       <c r="C52" s="24"/>
       <c r="D52" s="25"/>
       <c r="E52" s="24"/>
       <c r="F52" s="23"/>
       <c r="G52" s="22"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="13"/>
-    </row>
-    <row r="53" spans="2:10">
+      <c r="H52" s="22"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="13"/>
+    </row>
+    <row r="53" spans="2:11">
       <c r="B53" s="26"/>
       <c r="C53" s="24"/>
       <c r="D53" s="25"/>
       <c r="E53" s="24"/>
       <c r="F53" s="23"/>
       <c r="G53" s="22"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="13"/>
-    </row>
-    <row r="54" spans="2:10">
+      <c r="H53" s="22"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="13"/>
+    </row>
+    <row r="54" spans="2:11">
       <c r="B54" s="26"/>
       <c r="C54" s="24"/>
       <c r="D54" s="25"/>
       <c r="E54" s="24"/>
       <c r="F54" s="23"/>
       <c r="G54" s="22"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="13"/>
-    </row>
-    <row r="55" spans="2:10">
+      <c r="H54" s="22"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="13"/>
+    </row>
+    <row r="55" spans="2:11">
       <c r="B55" s="26"/>
       <c r="C55" s="24"/>
       <c r="D55" s="25"/>
       <c r="E55" s="24"/>
       <c r="F55" s="23"/>
       <c r="G55" s="22"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="13"/>
-    </row>
-    <row r="56" spans="2:10">
+      <c r="H55" s="22"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="13"/>
+    </row>
+    <row r="56" spans="2:11">
       <c r="B56" s="26"/>
       <c r="C56" s="24"/>
       <c r="D56" s="25"/>
       <c r="E56" s="24"/>
       <c r="F56" s="23"/>
       <c r="G56" s="22"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="13"/>
-    </row>
-    <row r="57" spans="2:10">
+      <c r="H56" s="22"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="13"/>
+    </row>
+    <row r="57" spans="2:11">
       <c r="B57" s="26"/>
       <c r="C57" s="24"/>
       <c r="D57" s="25"/>
       <c r="E57" s="24"/>
       <c r="F57" s="23"/>
       <c r="G57" s="22"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="13"/>
-    </row>
-    <row r="58" spans="2:10">
+      <c r="H57" s="22"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" spans="2:11">
       <c r="B58" s="20"/>
       <c r="C58" s="18"/>
       <c r="D58" s="19"/>
       <c r="E58" s="18"/>
       <c r="F58" s="17"/>
       <c r="G58" s="16"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" spans="2:10">
+      <c r="H58" s="16"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="13"/>
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59" s="12"/>
       <c r="C59" s="11"/>
       <c r="D59" s="6"/>
       <c r="E59" s="11"/>
       <c r="F59" s="10"/>
       <c r="G59" s="9"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="7"/>
-    </row>
-    <row r="61" spans="2:10" ht="27" customHeight="1"/>
-    <row r="110" spans="2:2">
+      <c r="H59" s="9"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="7"/>
+    </row>
+    <row r="61" spans="2:11" ht="27" customHeight="1"/>
+    <row r="110" spans="2:8" s="4" customFormat="1">
       <c r="B110" s="5"/>
-    </row>
-    <row r="111" spans="2:2">
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+    </row>
+    <row r="111" spans="2:8" s="4" customFormat="1">
       <c r="B111" s="5"/>
-    </row>
-    <row r="112" spans="2:2">
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+    </row>
+    <row r="112" spans="2:8" s="4" customFormat="1">
       <c r="B112" s="6"/>
-    </row>
-    <row r="113" spans="2:2">
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+    </row>
+    <row r="113" spans="2:8" s="4" customFormat="1">
       <c r="B113" s="5"/>
-    </row>
-    <row r="114" spans="2:2">
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+    </row>
+    <row r="114" spans="2:8" s="4" customFormat="1">
       <c r="B114" s="6"/>
-    </row>
-    <row r="115" spans="2:2">
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+    </row>
+    <row r="115" spans="2:8" s="4" customFormat="1">
       <c r="B115" s="5"/>
-    </row>
-    <row r="116" spans="2:2">
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+    </row>
+    <row r="116" spans="2:8" s="4" customFormat="1">
       <c r="B116" s="6"/>
-    </row>
-    <row r="117" spans="2:2">
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+    </row>
+    <row r="117" spans="2:8" s="4" customFormat="1">
       <c r="B117" s="5"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3488,7 +4618,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>入力規則!$A:$A</xm:f>
           </x14:formula1>
@@ -3502,1224 +4632,687 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:J117"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12" style="4" customWidth="1"/>
-    <col min="4" max="4" width="19.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="7.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="41.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="20.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="9.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.75" style="3" customWidth="1"/>
+    <col min="6" max="8" width="7.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="41.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="36"/>
       <c r="B2" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="21.75" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="21.75" customHeight="1">
       <c r="B3" s="34" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>173</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="B4" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="28">
-        <v>5.12</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="26"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="27"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="B5" s="26">
-        <v>43041</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="28">
-        <v>6.03</v>
-      </c>
+      <c r="H4" s="27"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="33"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" s="26"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="28"/>
       <c r="G5" s="27"/>
-      <c r="H5" s="32">
-        <v>3</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="26">
-        <v>43041</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="28">
-        <v>6.03</v>
-      </c>
+      <c r="H5" s="27"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="26"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="28"/>
       <c r="G6" s="27"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="B7" s="26">
-        <v>43044</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="H6" s="27"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="26"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="24"/>
       <c r="F7" s="28"/>
-      <c r="G7" s="27">
-        <v>4</v>
-      </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="B8" s="26">
-        <v>43045</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="28">
-        <v>6.03</v>
-      </c>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="26"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="28"/>
       <c r="G8" s="27"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="B9" s="26">
-        <v>43054</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="28">
-        <v>5</v>
-      </c>
+      <c r="H8" s="27"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="26"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="28"/>
       <c r="G9" s="27"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10" s="26">
-        <v>43055</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="28">
-        <v>6.03</v>
-      </c>
+      <c r="H9" s="27"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="26"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="28"/>
       <c r="G10" s="27"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="B11" s="26">
-        <v>43047</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="28">
-        <v>8.2219999999999995</v>
-      </c>
+      <c r="H10" s="27"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="26"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="27"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="B12" s="26">
-        <v>43046</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="H11" s="27"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="26"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="27">
-        <v>5</v>
-      </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" s="26">
-        <v>43062</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>33</v>
-      </c>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="26"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="28"/>
-      <c r="G13" s="27">
-        <v>1</v>
-      </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" s="26">
-        <v>43045</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="28">
-        <v>8</v>
-      </c>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="26"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="27"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="B15" s="26">
-        <v>43048</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="28">
-        <v>8</v>
-      </c>
+      <c r="H14" s="27"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="26"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="27"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="B16" s="26">
-        <v>43048</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="28">
-        <v>8</v>
-      </c>
+      <c r="H15" s="27"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="26"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="27"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="28">
-        <v>5</v>
-      </c>
+      <c r="H16" s="27"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="26"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="28"/>
       <c r="G17" s="27"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="28">
-        <v>5</v>
-      </c>
+      <c r="H17" s="27"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="26"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="28"/>
       <c r="G18" s="27"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="28">
-        <v>5</v>
-      </c>
+      <c r="H18" s="27"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="26"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="28"/>
       <c r="G19" s="27"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="28">
-        <v>5</v>
-      </c>
+      <c r="H19" s="27"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="26"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="28"/>
       <c r="G20" s="27"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="28">
-        <v>5</v>
-      </c>
+      <c r="H20" s="27"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="26"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="28"/>
       <c r="G21" s="27"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="28">
-        <v>5</v>
-      </c>
+      <c r="H21" s="27"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="26"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="28"/>
       <c r="G22" s="27"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="28">
-        <v>5</v>
-      </c>
+      <c r="H22" s="27"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="26"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="28"/>
       <c r="G23" s="27"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="28">
-        <v>5</v>
-      </c>
+      <c r="H23" s="27"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" s="26"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="28"/>
       <c r="G24" s="27"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="28">
-        <v>5</v>
-      </c>
+      <c r="H24" s="27"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" s="26"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="28"/>
       <c r="G25" s="27"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B26" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="28">
-        <v>5</v>
-      </c>
+      <c r="H25" s="27"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="2:10" ht="14.25" customHeight="1">
+      <c r="B26" s="26"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="28"/>
       <c r="G26" s="27"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="28">
-        <v>5</v>
-      </c>
+      <c r="H26" s="27"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27" s="26"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="28"/>
       <c r="G27" s="27"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="28">
-        <v>5</v>
-      </c>
+      <c r="H27" s="27"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28" s="26"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="28"/>
       <c r="G28" s="27"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="28">
-        <v>5</v>
-      </c>
+      <c r="H28" s="27"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="26"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="28"/>
       <c r="G29" s="27"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="14"/>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="28">
-        <v>5</v>
-      </c>
+      <c r="H29" s="27"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="26"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="28"/>
       <c r="G30" s="27"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="28">
-        <v>5</v>
-      </c>
+      <c r="H30" s="27"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31" s="26"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="27"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="28">
-        <v>5</v>
-      </c>
+      <c r="H31" s="27"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32" s="26"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="28"/>
       <c r="G32" s="27"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="14"/>
-    </row>
-    <row r="33" spans="2:9">
-      <c r="B33" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="28">
-        <v>5</v>
-      </c>
+      <c r="H32" s="27"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" s="26"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="28"/>
       <c r="G33" s="27"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9">
-      <c r="B34" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="28">
-        <v>5</v>
-      </c>
+      <c r="H33" s="27"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34" s="26"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="28"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="14"/>
-    </row>
-    <row r="35" spans="2:9">
-      <c r="B35" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="28">
-        <v>5</v>
-      </c>
+      <c r="H34" s="27"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="26"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="28"/>
       <c r="G35" s="27"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="14"/>
-    </row>
-    <row r="36" spans="2:9">
-      <c r="B36" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="28">
-        <v>5</v>
-      </c>
+      <c r="H35" s="27"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36" s="26"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="28"/>
       <c r="G36" s="27"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="14"/>
-    </row>
-    <row r="37" spans="2:9">
-      <c r="B37" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="28">
-        <v>5</v>
-      </c>
+      <c r="H36" s="27"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37" s="26"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="28"/>
       <c r="G37" s="27"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="14"/>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="B38" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="28">
-        <v>5</v>
-      </c>
+      <c r="H37" s="27"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="B38" s="26"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="28"/>
       <c r="G38" s="27"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="14"/>
-    </row>
-    <row r="39" spans="2:9">
-      <c r="B39" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="28">
-        <v>5</v>
-      </c>
+      <c r="H38" s="27"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="B39" s="26"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="28"/>
       <c r="G39" s="27"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="14"/>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="28">
-        <v>5</v>
-      </c>
+      <c r="H39" s="27"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40" s="26"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="28"/>
       <c r="G40" s="27"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="14"/>
-    </row>
-    <row r="41" spans="2:9">
-      <c r="B41" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E41" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="28">
-        <v>5</v>
-      </c>
+      <c r="H40" s="27"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="26"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="28"/>
       <c r="G41" s="27"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="28">
-        <v>5</v>
-      </c>
+      <c r="H41" s="27"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="26"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="28"/>
       <c r="G42" s="27"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9">
-      <c r="B43" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="23">
-        <v>5</v>
-      </c>
+      <c r="H42" s="27"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="26"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="23"/>
       <c r="G43" s="22"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="28">
-        <v>5</v>
-      </c>
+      <c r="H43" s="22"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="14"/>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44" s="26"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="28"/>
       <c r="G44" s="27"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9">
-      <c r="B45" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="28">
-        <v>5</v>
-      </c>
+      <c r="H44" s="27"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45" s="26"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="28"/>
       <c r="G45" s="27"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="28">
-        <v>5</v>
-      </c>
+      <c r="H45" s="27"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="26"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="28"/>
       <c r="G46" s="27"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9">
-      <c r="B47" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="23">
-        <v>5</v>
-      </c>
+      <c r="H46" s="27"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="B47" s="26"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="23"/>
       <c r="G47" s="22"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="23">
-        <v>5</v>
-      </c>
+      <c r="H47" s="22"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="2:10">
+      <c r="B48" s="26"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="22"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="B49" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="23">
-        <v>5</v>
-      </c>
+      <c r="H48" s="22"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="2:11">
+      <c r="B49" s="26"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="23"/>
       <c r="G49" s="22"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" s="13" customFormat="1">
-      <c r="B50" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="23">
-        <v>5</v>
-      </c>
+      <c r="H49" s="22"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="2:11" s="13" customFormat="1">
+      <c r="B50" s="26"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="23"/>
       <c r="G50" s="22"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="23">
-        <v>5</v>
-      </c>
+      <c r="H50" s="22"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="26"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="23"/>
       <c r="G51" s="22"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="13"/>
-    </row>
-    <row r="52" spans="2:10">
-      <c r="B52" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E52" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="23">
-        <v>5</v>
-      </c>
+      <c r="H51" s="22"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52" s="26"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="23"/>
       <c r="G52" s="22"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" s="13"/>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F53" s="23">
-        <v>5</v>
-      </c>
+      <c r="H52" s="22"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="13"/>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53" s="26"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="23"/>
       <c r="G53" s="22"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J53" s="13"/>
-    </row>
-    <row r="54" spans="2:10">
-      <c r="B54" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="23">
-        <v>5</v>
-      </c>
+      <c r="H53" s="22"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="13"/>
+    </row>
+    <row r="54" spans="2:11">
+      <c r="B54" s="26"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="23"/>
       <c r="G54" s="22"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="13"/>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="23">
-        <v>5</v>
-      </c>
+      <c r="H54" s="22"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="13"/>
+    </row>
+    <row r="55" spans="2:11">
+      <c r="B55" s="26"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="23"/>
       <c r="G55" s="22"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J55" s="13"/>
-    </row>
-    <row r="56" spans="2:10">
-      <c r="B56" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="23">
-        <v>5</v>
-      </c>
+      <c r="H55" s="22"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="13"/>
+    </row>
+    <row r="56" spans="2:11">
+      <c r="B56" s="26"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="23"/>
       <c r="G56" s="22"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J56" s="13"/>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="23">
-        <v>5</v>
-      </c>
+      <c r="H56" s="22"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="13"/>
+    </row>
+    <row r="57" spans="2:11">
+      <c r="B57" s="26"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="23"/>
       <c r="G57" s="22"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J57" s="13"/>
-    </row>
-    <row r="58" spans="2:10">
-      <c r="B58" s="20">
-        <v>43040</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" s="17">
-        <v>5</v>
-      </c>
+      <c r="H57" s="22"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" s="20"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="17"/>
       <c r="G58" s="16"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" spans="2:10">
+      <c r="H58" s="16"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="13"/>
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59" s="12"/>
       <c r="C59" s="11"/>
       <c r="D59" s="6"/>
       <c r="E59" s="11"/>
       <c r="F59" s="10"/>
       <c r="G59" s="9"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="7"/>
-    </row>
-    <row r="61" spans="2:10" ht="27" customHeight="1"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="7"/>
+    </row>
+    <row r="61" spans="2:11" ht="27" customHeight="1"/>
     <row r="110" spans="2:2">
       <c r="B110" s="5"/>
     </row>
@@ -4758,7 +5351,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>入力規則!$A:$A</xm:f>
           </x14:formula1>
@@ -4772,675 +5365,765 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:J117"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:K97"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12" style="4" customWidth="1"/>
-    <col min="4" max="4" width="19.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="7.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="41.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="20.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="9.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.75" style="3" customWidth="1"/>
+    <col min="6" max="8" width="7.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="41.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="36"/>
       <c r="B2" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="21.75" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="21.75" customHeight="1">
       <c r="B3" s="34" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>172</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>41</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4" s="26">
-        <v>43040</v>
+        <v>42919</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="F4" s="28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="27"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="H4" s="27"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="33"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5" s="26">
-        <v>43040</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>2</v>
-      </c>
+        <v>42919</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="24" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="F5" s="28">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="G5" s="27"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="26"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="26">
+        <v>42919</v>
+      </c>
       <c r="C6" s="24"/>
       <c r="D6" s="31"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="28"/>
+      <c r="E6" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G6" s="27"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="B7" s="26"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="28"/>
+      <c r="H6" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="I6" s="21">
+        <v>9.9</v>
+      </c>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="26">
+        <v>42920</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="28">
+        <v>6</v>
+      </c>
       <c r="G7" s="27"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="B8" s="26"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="28"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="26">
+        <v>42920</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="28">
+        <v>1.2</v>
+      </c>
       <c r="G8" s="27"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="B9" s="26"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="26">
+        <v>42920</v>
+      </c>
       <c r="C9" s="24"/>
       <c r="D9" s="25"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="28"/>
+      <c r="E9" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G9" s="27"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10" s="26"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="28"/>
+      <c r="H9" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="I9" s="21"/>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="26">
+        <v>42921</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="28">
+        <v>7.7</v>
+      </c>
       <c r="G10" s="27"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="B11" s="26"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="28"/>
+      <c r="H10" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="I10" s="21"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="26">
+        <v>42922</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="28">
+        <v>1</v>
+      </c>
       <c r="G11" s="27"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="B12" s="26"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="28"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="26">
+        <v>42922</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="28">
+        <v>2.7</v>
+      </c>
       <c r="G12" s="27"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" s="26"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="28"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="26">
+        <v>42922</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="28">
+        <v>4</v>
+      </c>
       <c r="G13" s="27"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" s="26"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="28"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="26">
+        <v>42923</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="28">
+        <v>7.7</v>
+      </c>
       <c r="G14" s="27"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="B15" s="26"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="25"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="26">
+        <v>42926</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>122</v>
+      </c>
       <c r="E15" s="24"/>
-      <c r="F15" s="28"/>
+      <c r="F15" s="28">
+        <v>8.6999999999999993</v>
+      </c>
       <c r="G15" s="27"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="14"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="B16" s="26"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="14" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="26">
+        <v>42926</v>
+      </c>
       <c r="C16" s="24"/>
       <c r="D16" s="25"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="28"/>
+      <c r="E16" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G16" s="27"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="26"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="28"/>
+      <c r="H16" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="I16" s="21"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" s="26">
+        <v>42927</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" s="28">
+        <v>5</v>
+      </c>
       <c r="G17" s="27"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="26"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="28"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="26">
+        <v>42927</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F18" s="28">
+        <v>5.7</v>
+      </c>
       <c r="G18" s="27"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="26"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" s="26">
+        <v>42927</v>
+      </c>
       <c r="C19" s="24"/>
       <c r="D19" s="25"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="28"/>
+      <c r="E19" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G19" s="27"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="26"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="28"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="26">
+        <v>42928</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="28">
+        <v>7.2</v>
+      </c>
       <c r="G20" s="27"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="26"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="26">
+        <v>42928</v>
+      </c>
       <c r="C21" s="24"/>
       <c r="D21" s="25"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="28"/>
+      <c r="E21" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G21" s="27"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="26"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="28"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="B22" s="26">
+        <v>42929</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="28">
+        <v>11.2</v>
+      </c>
       <c r="G22" s="27"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="26"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" s="26">
+        <v>42929</v>
+      </c>
       <c r="C23" s="24"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="28"/>
+      <c r="E23" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G23" s="27"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="26"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="28"/>
+      <c r="H23" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="I23" s="21"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" s="26">
+        <v>42930</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" s="28">
+        <v>8</v>
+      </c>
       <c r="G24" s="27"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" s="26"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="28"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="B25" s="26">
+        <v>42930</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="28">
+        <v>3.2</v>
+      </c>
       <c r="G25" s="27"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B26" s="26"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="26">
+        <v>42930</v>
+      </c>
       <c r="C26" s="24"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="28"/>
+      <c r="E26" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G26" s="27"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="26"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="26"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="28"/>
+      <c r="H26" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="I26" s="21"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27" s="26">
+        <v>42931</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="23">
+        <v>6</v>
+      </c>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="I27" s="21"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="26">
+        <v>42934</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F28" s="28">
+        <v>3.2</v>
+      </c>
       <c r="G28" s="27"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="26"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="14"/>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" s="26"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29" s="26">
+        <v>42934</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="23">
+        <v>8</v>
+      </c>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="26">
+        <v>42934</v>
+      </c>
       <c r="C30" s="24"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="26"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" s="26"/>
+      <c r="E30" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F30" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="I30" s="21"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="26">
+        <v>42935</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F31" s="23">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="21">
+        <v>3</v>
+      </c>
+      <c r="J31" s="14"/>
+      <c r="K31" s="13"/>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="26">
+        <v>42935</v>
+      </c>
       <c r="C32" s="24"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="14"/>
-    </row>
-    <row r="33" spans="2:9">
+      <c r="E32" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="K32" s="13"/>
+    </row>
+    <row r="33" spans="2:11">
       <c r="B33" s="26"/>
       <c r="C33" s="24"/>
       <c r="D33" s="25"/>
       <c r="E33" s="24"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="14"/>
-    </row>
-    <row r="34" spans="2:9">
+      <c r="F33" s="23"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="13"/>
+    </row>
+    <row r="34" spans="2:11">
       <c r="B34" s="26"/>
       <c r="C34" s="24"/>
       <c r="D34" s="25"/>
       <c r="E34" s="24"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="14"/>
-    </row>
-    <row r="35" spans="2:9">
+      <c r="F34" s="23"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="13"/>
+    </row>
+    <row r="35" spans="2:11">
       <c r="B35" s="26"/>
       <c r="C35" s="24"/>
       <c r="D35" s="25"/>
       <c r="E35" s="24"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="14"/>
-    </row>
-    <row r="36" spans="2:9">
+      <c r="F35" s="23"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="13"/>
+    </row>
+    <row r="36" spans="2:11">
       <c r="B36" s="26"/>
       <c r="C36" s="24"/>
       <c r="D36" s="25"/>
       <c r="E36" s="24"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="14"/>
-    </row>
-    <row r="37" spans="2:9">
+      <c r="F36" s="23"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="13"/>
+    </row>
+    <row r="37" spans="2:11">
       <c r="B37" s="26"/>
       <c r="C37" s="24"/>
       <c r="D37" s="25"/>
       <c r="E37" s="24"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="14"/>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="B38" s="26"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="14"/>
-    </row>
-    <row r="39" spans="2:9">
-      <c r="B39" s="26"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="14"/>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="26"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="14"/>
-    </row>
-    <row r="41" spans="2:9">
-      <c r="B41" s="26"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="14"/>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="26"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="14"/>
-    </row>
-    <row r="43" spans="2:9">
-      <c r="B43" s="26"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="14"/>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="26"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="14"/>
-    </row>
-    <row r="45" spans="2:9">
-      <c r="B45" s="26"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="14"/>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="26"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="14"/>
-    </row>
-    <row r="47" spans="2:9">
-      <c r="B47" s="26"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="14"/>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="26"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="14"/>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="B49" s="26"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="14"/>
-    </row>
-    <row r="50" spans="2:10" s="13" customFormat="1">
-      <c r="B50" s="26"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="26"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="13"/>
-    </row>
-    <row r="52" spans="2:10">
-      <c r="B52" s="26"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="13"/>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" s="26"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="13"/>
-    </row>
-    <row r="54" spans="2:10">
-      <c r="B54" s="26"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="13"/>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" s="26"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="13"/>
-    </row>
-    <row r="56" spans="2:10">
-      <c r="B56" s="26"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="13"/>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" s="26"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="13"/>
-    </row>
-    <row r="58" spans="2:10">
-      <c r="B58" s="20"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" spans="2:10">
-      <c r="B59" s="12"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="7"/>
-    </row>
-    <row r="61" spans="2:10" ht="27" customHeight="1"/>
-    <row r="110" spans="2:2">
-      <c r="B110" s="5"/>
-    </row>
-    <row r="111" spans="2:2">
-      <c r="B111" s="5"/>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112" s="6"/>
-    </row>
-    <row r="113" spans="2:2">
-      <c r="B113" s="5"/>
-    </row>
-    <row r="114" spans="2:2">
-      <c r="B114" s="6"/>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="5"/>
-    </row>
-    <row r="116" spans="2:2">
-      <c r="B116" s="6"/>
-    </row>
-    <row r="117" spans="2:2">
-      <c r="B117" s="5"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="13"/>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38" s="20"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39" s="12"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="7"/>
+    </row>
+    <row r="41" spans="2:11" ht="27" customHeight="1"/>
+    <row r="90" spans="2:2">
+      <c r="B90" s="5"/>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="5"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="6"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="5"/>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="6"/>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="5"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="6"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5456,11 +6139,11 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>入力規則!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>E4:E58</xm:sqref>
+          <xm:sqref>E4:E38</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5470,285 +6153,291 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:J117"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="3" customWidth="1"/>
     <col min="3" max="3" width="12" style="4" customWidth="1"/>
     <col min="4" max="4" width="19.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="7.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="41.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="6" max="8" width="7.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="41.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="36"/>
       <c r="B2" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="21.75" customHeight="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="21.75" customHeight="1">
       <c r="B3" s="34" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>173</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>41</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4" s="26">
         <v>43040</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="F4" s="28">
         <v>5.12</v>
       </c>
       <c r="G4" s="27"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="33" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="H4" s="27"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5" s="26">
         <v>43041</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="F5" s="28">
         <v>6.03</v>
       </c>
       <c r="G5" s="27"/>
-      <c r="H5" s="32">
+      <c r="H5" s="27"/>
+      <c r="I5" s="32">
         <v>3</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="26">
         <v>43041</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>77</v>
+        <v>50</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="F6" s="28">
         <v>6.03</v>
       </c>
       <c r="G6" s="27"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="H6" s="27"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7" s="26">
         <v>43044</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>79</v>
-      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="24" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" s="27">
         <v>4</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="H7" s="27"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" s="26">
         <v>43045</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>79</v>
-      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
       <c r="E8" s="24" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="F8" s="28">
         <v>6.03</v>
       </c>
       <c r="G8" s="27"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="H8" s="27"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="26">
         <v>43054</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" s="28">
         <v>5</v>
       </c>
       <c r="G9" s="27"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="H9" s="27"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10" s="26">
         <v>43055</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>2</v>
+        <v>139</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>140</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="F10" s="28">
         <v>6.03</v>
       </c>
       <c r="G10" s="27"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="H10" s="27"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11" s="26">
         <v>43047</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="F11" s="28">
         <v>8.2219999999999995</v>
       </c>
       <c r="G11" s="27"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="H11" s="27"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" s="26">
         <v>43046</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="F12" s="28"/>
       <c r="G12" s="27">
         <v>5</v>
       </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="H12" s="27"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" s="26">
         <v>43062</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" s="27">
         <v>1</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="H13" s="27"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="26">
         <v>43045</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="F14" s="28">
         <v>8</v>
       </c>
       <c r="G14" s="27"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="H14" s="27"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15" s="26">
         <v>43048</v>
       </c>
@@ -5765,32 +6454,34 @@
         <v>8</v>
       </c>
       <c r="G15" s="27"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="H15" s="27"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16" s="26">
         <v>43048</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="F16" s="28">
         <v>8</v>
       </c>
       <c r="G16" s="27"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="2:9">
+      <c r="H16" s="27"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17" s="26">
         <v>43040</v>
       </c>
@@ -5807,15 +6498,16 @@
         <v>5</v>
       </c>
       <c r="G17" s="27"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="2:9">
+      <c r="H17" s="27"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18" s="26">
         <v>43040</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D18" s="25" t="s">
         <v>2</v>
@@ -5827,15 +6519,16 @@
         <v>5</v>
       </c>
       <c r="G18" s="27"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="2:9">
+      <c r="H18" s="27"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19" s="26">
         <v>43040</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D19" s="25" t="s">
         <v>2</v>
@@ -5847,15 +6540,16 @@
         <v>5</v>
       </c>
       <c r="G19" s="27"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="2:9">
+      <c r="H19" s="27"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20" s="26">
         <v>43040</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D20" s="25" t="s">
         <v>2</v>
@@ -5867,15 +6561,16 @@
         <v>5</v>
       </c>
       <c r="G20" s="27"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="2:9">
+      <c r="H20" s="27"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21" s="26">
         <v>43040</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D21" s="25" t="s">
         <v>2</v>
@@ -5887,15 +6582,16 @@
         <v>5</v>
       </c>
       <c r="G21" s="27"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="2:9">
+      <c r="H21" s="27"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="2:10">
       <c r="B22" s="26">
         <v>43040</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D22" s="25" t="s">
         <v>2</v>
@@ -5907,15 +6603,16 @@
         <v>5</v>
       </c>
       <c r="G22" s="27"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="2:9">
+      <c r="H22" s="27"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="2:10">
       <c r="B23" s="26">
         <v>43040</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D23" s="25" t="s">
         <v>2</v>
@@ -5927,15 +6624,16 @@
         <v>5</v>
       </c>
       <c r="G23" s="27"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="2:9">
+      <c r="H23" s="27"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="2:10">
       <c r="B24" s="26">
         <v>43040</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D24" s="25" t="s">
         <v>2</v>
@@ -5947,15 +6645,16 @@
         <v>5</v>
       </c>
       <c r="G24" s="27"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" spans="2:9">
+      <c r="H24" s="27"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="2:10">
       <c r="B25" s="26">
         <v>43040</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D25" s="25" t="s">
         <v>2</v>
@@ -5967,15 +6666,16 @@
         <v>5</v>
       </c>
       <c r="G25" s="27"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="2:9" ht="14.25" customHeight="1">
+      <c r="H25" s="27"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="2:10" ht="14.25" customHeight="1">
       <c r="B26" s="26">
         <v>43040</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D26" s="25" t="s">
         <v>2</v>
@@ -5987,15 +6687,16 @@
         <v>5</v>
       </c>
       <c r="G26" s="27"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" spans="2:9">
+      <c r="H26" s="27"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="2:10">
       <c r="B27" s="26">
         <v>43040</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D27" s="25" t="s">
         <v>2</v>
@@ -6007,15 +6708,16 @@
         <v>5</v>
       </c>
       <c r="G27" s="27"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" spans="2:9">
+      <c r="H27" s="27"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="2:10">
       <c r="B28" s="26">
         <v>43040</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D28" s="25" t="s">
         <v>2</v>
@@ -6027,15 +6729,16 @@
         <v>5</v>
       </c>
       <c r="G28" s="27"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" spans="2:9">
+      <c r="H28" s="27"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="2:10">
       <c r="B29" s="26">
         <v>43040</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D29" s="25" t="s">
         <v>2</v>
@@ -6047,15 +6750,16 @@
         <v>5</v>
       </c>
       <c r="G29" s="27"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="14"/>
-    </row>
-    <row r="30" spans="2:9">
+      <c r="H29" s="27"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="2:10">
       <c r="B30" s="26">
         <v>43040</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D30" s="25" t="s">
         <v>2</v>
@@ -6067,15 +6771,16 @@
         <v>5</v>
       </c>
       <c r="G30" s="27"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" spans="2:9">
+      <c r="H30" s="27"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="2:10">
       <c r="B31" s="26">
         <v>43040</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D31" s="25" t="s">
         <v>2</v>
@@ -6087,15 +6792,16 @@
         <v>5</v>
       </c>
       <c r="G31" s="27"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="2:9">
+      <c r="H31" s="27"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="2:10">
       <c r="B32" s="26">
         <v>43040</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D32" s="25" t="s">
         <v>2</v>
@@ -6107,15 +6813,16 @@
         <v>5</v>
       </c>
       <c r="G32" s="27"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="14"/>
-    </row>
-    <row r="33" spans="2:9">
+      <c r="H32" s="27"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="2:10">
       <c r="B33" s="26">
         <v>43040</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D33" s="25" t="s">
         <v>2</v>
@@ -6127,17 +6834,18 @@
         <v>5</v>
       </c>
       <c r="G33" s="27"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9">
+      <c r="H33" s="27"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34" s="26">
         <v>43040</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D34" s="25" t="s">
         <v>2</v>
@@ -6149,15 +6857,16 @@
         <v>5</v>
       </c>
       <c r="G34" s="27"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="14"/>
-    </row>
-    <row r="35" spans="2:9">
+      <c r="H34" s="27"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="2:10">
       <c r="B35" s="26">
         <v>43040</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D35" s="25" t="s">
         <v>2</v>
@@ -6169,10 +6878,11 @@
         <v>5</v>
       </c>
       <c r="G35" s="27"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="14"/>
-    </row>
-    <row r="36" spans="2:9">
+      <c r="H35" s="27"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36" s="26">
         <v>43040</v>
       </c>
@@ -6189,10 +6899,11 @@
         <v>5</v>
       </c>
       <c r="G36" s="27"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="14"/>
-    </row>
-    <row r="37" spans="2:9">
+      <c r="H36" s="27"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="2:10">
       <c r="B37" s="26">
         <v>43040</v>
       </c>
@@ -6209,10 +6920,11 @@
         <v>5</v>
       </c>
       <c r="G37" s="27"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="14"/>
-    </row>
-    <row r="38" spans="2:9">
+      <c r="H37" s="27"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="2:10">
       <c r="B38" s="26">
         <v>43040</v>
       </c>
@@ -6229,10 +6941,11 @@
         <v>5</v>
       </c>
       <c r="G38" s="27"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="14"/>
-    </row>
-    <row r="39" spans="2:9">
+      <c r="H38" s="27"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="2:10">
       <c r="B39" s="26">
         <v>43040</v>
       </c>
@@ -6249,10 +6962,11 @@
         <v>5</v>
       </c>
       <c r="G39" s="27"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="14"/>
-    </row>
-    <row r="40" spans="2:9">
+      <c r="H39" s="27"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="2:10">
       <c r="B40" s="26">
         <v>43040</v>
       </c>
@@ -6269,10 +6983,11 @@
         <v>5</v>
       </c>
       <c r="G40" s="27"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="14"/>
-    </row>
-    <row r="41" spans="2:9">
+      <c r="H40" s="27"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="2:10">
       <c r="B41" s="26">
         <v>43040</v>
       </c>
@@ -6289,12 +7004,13 @@
         <v>5</v>
       </c>
       <c r="G41" s="27"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9">
+      <c r="H41" s="27"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
       <c r="B42" s="26">
         <v>43040</v>
       </c>
@@ -6311,12 +7027,13 @@
         <v>5</v>
       </c>
       <c r="G42" s="27"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9">
+      <c r="H42" s="27"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
       <c r="B43" s="26">
         <v>43040</v>
       </c>
@@ -6333,12 +7050,13 @@
         <v>5</v>
       </c>
       <c r="G43" s="22"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9">
+      <c r="H43" s="22"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
       <c r="B44" s="26">
         <v>43040</v>
       </c>
@@ -6355,12 +7073,13 @@
         <v>5</v>
       </c>
       <c r="G44" s="27"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9">
+      <c r="H44" s="27"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
       <c r="B45" s="26">
         <v>43040</v>
       </c>
@@ -6377,12 +7096,13 @@
         <v>5</v>
       </c>
       <c r="G45" s="27"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9">
+      <c r="H45" s="27"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
       <c r="B46" s="26">
         <v>43040</v>
       </c>
@@ -6399,12 +7119,13 @@
         <v>5</v>
       </c>
       <c r="G46" s="27"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9">
+      <c r="H46" s="27"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
       <c r="B47" s="26">
         <v>43040</v>
       </c>
@@ -6421,12 +7142,13 @@
         <v>5</v>
       </c>
       <c r="G47" s="22"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="14" t="s">
+      <c r="H47" s="22"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:10">
       <c r="B48" s="26">
         <v>43040</v>
       </c>
@@ -6443,12 +7165,13 @@
         <v>5</v>
       </c>
       <c r="G48" s="22"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="14" t="s">
+      <c r="H48" s="22"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="2:10">
+    <row r="49" spans="2:11">
       <c r="B49" s="26">
         <v>43040</v>
       </c>
@@ -6465,12 +7188,13 @@
         <v>5</v>
       </c>
       <c r="G49" s="22"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="14" t="s">
+      <c r="H49" s="22"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="2:10" s="13" customFormat="1">
+    <row r="50" spans="2:11" s="13" customFormat="1">
       <c r="B50" s="26">
         <v>43040</v>
       </c>
@@ -6487,13 +7211,14 @@
         <v>5</v>
       </c>
       <c r="G50" s="22"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="14" t="s">
+      <c r="H50" s="22"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="2:10">
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" spans="2:11">
       <c r="B51" s="26">
         <v>43040</v>
       </c>
@@ -6510,13 +7235,14 @@
         <v>5</v>
       </c>
       <c r="G51" s="22"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="14" t="s">
+      <c r="H51" s="22"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="13"/>
-    </row>
-    <row r="52" spans="2:10">
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" spans="2:11">
       <c r="B52" s="26">
         <v>43040</v>
       </c>
@@ -6524,7 +7250,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>10</v>
@@ -6533,13 +7259,14 @@
         <v>5</v>
       </c>
       <c r="G52" s="22"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="14" t="s">
+      <c r="H52" s="22"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="J52" s="13"/>
-    </row>
-    <row r="53" spans="2:10">
+      <c r="K52" s="13"/>
+    </row>
+    <row r="53" spans="2:11">
       <c r="B53" s="26">
         <v>43040</v>
       </c>
@@ -6550,19 +7277,20 @@
         <v>7</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="F53" s="23">
         <v>5</v>
       </c>
       <c r="G53" s="22"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="14" t="s">
+      <c r="H53" s="22"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J53" s="13"/>
-    </row>
-    <row r="54" spans="2:10">
+      <c r="K53" s="13"/>
+    </row>
+    <row r="54" spans="2:11">
       <c r="B54" s="26">
         <v>43040</v>
       </c>
@@ -6579,13 +7307,14 @@
         <v>5</v>
       </c>
       <c r="G54" s="22"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="14" t="s">
+      <c r="H54" s="22"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J54" s="13"/>
-    </row>
-    <row r="55" spans="2:10">
+      <c r="K54" s="13"/>
+    </row>
+    <row r="55" spans="2:11">
       <c r="B55" s="26">
         <v>43040</v>
       </c>
@@ -6602,13 +7331,14 @@
         <v>5</v>
       </c>
       <c r="G55" s="22"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="14" t="s">
+      <c r="H55" s="22"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J55" s="13"/>
-    </row>
-    <row r="56" spans="2:10">
+      <c r="K55" s="13"/>
+    </row>
+    <row r="56" spans="2:11">
       <c r="B56" s="26">
         <v>43040</v>
       </c>
@@ -6625,13 +7355,14 @@
         <v>5</v>
       </c>
       <c r="G56" s="22"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="14" t="s">
+      <c r="H56" s="22"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="J56" s="13"/>
-    </row>
-    <row r="57" spans="2:10">
+      <c r="K56" s="13"/>
+    </row>
+    <row r="57" spans="2:11">
       <c r="B57" s="26">
         <v>43040</v>
       </c>
@@ -6648,13 +7379,14 @@
         <v>5</v>
       </c>
       <c r="G57" s="22"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="14" t="s">
+      <c r="H57" s="22"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J57" s="13"/>
-    </row>
-    <row r="58" spans="2:10">
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" spans="2:11">
       <c r="B58" s="20">
         <v>43040</v>
       </c>
@@ -6665,29 +7397,31 @@
         <v>7</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F58" s="17">
         <v>5</v>
       </c>
       <c r="G58" s="16"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="14" t="s">
+      <c r="H58" s="16"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" spans="2:10">
+      <c r="K58" s="13"/>
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59" s="12"/>
       <c r="C59" s="11"/>
       <c r="D59" s="6"/>
       <c r="E59" s="11"/>
       <c r="F59" s="10"/>
       <c r="G59" s="9"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="7"/>
-    </row>
-    <row r="61" spans="2:10" ht="27" customHeight="1"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="7"/>
+    </row>
+    <row r="61" spans="2:11" ht="27" customHeight="1"/>
     <row r="110" spans="2:2">
       <c r="B110" s="5"/>
     </row>
@@ -6726,7 +7460,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>入力規則!$A:$A</xm:f>
           </x14:formula1>
@@ -6740,353 +7474,1130 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="3.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12" style="4" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="3" customWidth="1"/>
+    <col min="6" max="8" width="7.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="41.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="36"/>
+      <c r="B2" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="21.75" customHeight="1">
+      <c r="B3" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="28">
+        <v>5</v>
+      </c>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="28">
+        <v>5</v>
+      </c>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="26">
+        <v>43040</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="26"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="26"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="26"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="26"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="26"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="26"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="26"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="26"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="26"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="26"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="26"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="26"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="26"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="26"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="26"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="26"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="26"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" s="26"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" s="26"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="2:10" ht="14.25" customHeight="1">
+      <c r="B26" s="26"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27" s="26"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28" s="26"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="26"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="26"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31" s="26"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32" s="26"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" s="26"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34" s="26"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="26"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36" s="26"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37" s="26"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="B38" s="26"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="B39" s="26"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40" s="26"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="26"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="26"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="26"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="14"/>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44" s="26"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45" s="26"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="26"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="B47" s="26"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="2:10">
+      <c r="B48" s="26"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="2:11">
+      <c r="B49" s="26"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="2:11" s="13" customFormat="1">
+      <c r="B50" s="26"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="26"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52" s="26"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="13"/>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53" s="26"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="13"/>
+    </row>
+    <row r="54" spans="2:11">
+      <c r="B54" s="26"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="13"/>
+    </row>
+    <row r="55" spans="2:11">
+      <c r="B55" s="26"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="13"/>
+    </row>
+    <row r="56" spans="2:11">
+      <c r="B56" s="26"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="13"/>
+    </row>
+    <row r="57" spans="2:11">
+      <c r="B57" s="26"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" s="20"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="13"/>
+    </row>
+    <row r="59" spans="2:11">
+      <c r="B59" s="12"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="7"/>
+    </row>
+    <row r="61" spans="2:11" ht="27" customHeight="1"/>
+    <row r="110" spans="2:2">
+      <c r="B110" s="5"/>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="5"/>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="6"/>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="5"/>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" s="6"/>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="5"/>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="6"/>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="5"/>
+    </row>
+  </sheetData>
+  <sortState ref="A6:P59">
+    <sortCondition ref="A6"/>
+  </sortState>
+  <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>"社員,派遣"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="81" orientation="portrait" verticalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>入力規則!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>E4:E58</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A72"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="67.5">
-      <c r="A34" s="39" t="s">
-        <v>125</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>161</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
